--- a/results_(stress_test)_baselines_cross_valid/summary.xlsx
+++ b/results_(stress_test)_baselines_cross_valid/summary.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\RnD_Repo\Research_Engineering\feature_fusion_PCCxSigmoid-PLV-\results_(stress_test)_baselines\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\RnD_Repo\Research_Engineering\feature_fusion_PCCxSigmoid-PLV-\results_(stress_test)_baselines_cross_valid\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55B2D0DC-A473-480E-9EE7-404C7EC5E523}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B5BB243-AAD8-4123-8630-870E3C3C5F25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-210" windowWidth="29040" windowHeight="16440" tabRatio="639" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="639" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="partialdata_20260618_unf_idx" sheetId="6" r:id="rId1"/>
@@ -747,6 +747,87 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -756,58 +837,13 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -816,41 +852,20 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -866,21 +881,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1226,10 +1226,10 @@
       <c r="R1" s="12"/>
     </row>
     <row r="2" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="123" t="s">
+      <c r="A2" s="140" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="124"/>
+      <c r="B2" s="142"/>
       <c r="C2" s="114">
         <v>92.97270449283009</v>
       </c>
@@ -1257,10 +1257,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C2:G2)&amp;","</f>
         <v xml:space="preserve">    92.9727044928301, 92.6568511261632, 90.6124851137697, 76.8900480684666, 57.4311571322704,</v>
       </c>
-      <c r="K2" s="123" t="s">
+      <c r="K2" s="140" t="s">
         <v>5</v>
       </c>
-      <c r="L2" s="124"/>
+      <c r="L2" s="142"/>
       <c r="M2" s="77">
         <v>3.6723191410127392</v>
       </c>
@@ -1282,10 +1282,10 @@
       </c>
     </row>
     <row r="3" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="123" t="s">
+      <c r="A3" s="140" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="124"/>
+      <c r="B3" s="142"/>
       <c r="C3" s="117">
         <v>93.550650668835075</v>
       </c>
@@ -1313,10 +1313,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C3:G3)&amp;","</f>
         <v xml:space="preserve">    93.5506506688351, 92.2822198577266, 90.5016796569751, 72.8058085854261, 54.0640662981514,</v>
       </c>
-      <c r="K3" s="123" t="s">
+      <c r="K3" s="140" t="s">
         <v>6</v>
       </c>
-      <c r="L3" s="124"/>
+      <c r="L3" s="142"/>
       <c r="M3" s="80">
         <v>3.5444962758226279</v>
       </c>
@@ -1338,10 +1338,10 @@
       </c>
     </row>
     <row r="4" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="125" t="s">
+      <c r="A4" s="145" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="126"/>
+      <c r="B4" s="146"/>
       <c r="C4" s="117">
         <v>88.646029233240199</v>
       </c>
@@ -1369,10 +1369,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C4:G4)&amp;","</f>
         <v xml:space="preserve">    88.6460292332402, 87.5880039331367, 87.1022730877141, 74.8267141872623, 50.0552455759421,</v>
       </c>
-      <c r="K4" s="125" t="s">
+      <c r="K4" s="145" t="s">
         <v>10</v>
       </c>
-      <c r="L4" s="126"/>
+      <c r="L4" s="146"/>
       <c r="M4" s="80">
         <v>3.1531095164540388</v>
       </c>
@@ -1394,31 +1394,31 @@
       </c>
     </row>
     <row r="5" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="123" t="s">
+      <c r="A5" s="140" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="127"/>
-      <c r="C5" s="127"/>
-      <c r="D5" s="127"/>
-      <c r="E5" s="127"/>
-      <c r="F5" s="127"/>
-      <c r="G5" s="124"/>
+      <c r="B5" s="141"/>
+      <c r="C5" s="141"/>
+      <c r="D5" s="141"/>
+      <c r="E5" s="141"/>
+      <c r="F5" s="141"/>
+      <c r="G5" s="142"/>
       <c r="H5" s="34"/>
       <c r="I5" s="34"/>
       <c r="J5" s="12"/>
-      <c r="K5" s="123" t="s">
+      <c r="K5" s="140" t="s">
         <v>12</v>
       </c>
-      <c r="L5" s="127"/>
-      <c r="M5" s="127"/>
-      <c r="N5" s="127"/>
-      <c r="O5" s="127"/>
-      <c r="P5" s="127"/>
-      <c r="Q5" s="124"/>
+      <c r="L5" s="141"/>
+      <c r="M5" s="141"/>
+      <c r="N5" s="141"/>
+      <c r="O5" s="141"/>
+      <c r="P5" s="141"/>
+      <c r="Q5" s="142"/>
       <c r="R5" s="12"/>
     </row>
     <row r="6" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="125" t="s">
+      <c r="A6" s="145" t="s">
         <v>11</v>
       </c>
       <c r="B6" s="87" t="s">
@@ -1448,7 +1448,7 @@
         <v>83.954594024025582</v>
       </c>
       <c r="J6" s="12"/>
-      <c r="K6" s="125" t="s">
+      <c r="K6" s="145" t="s">
         <v>11</v>
       </c>
       <c r="L6" s="87" t="s">
@@ -1472,7 +1472,7 @@
       <c r="R6" s="12"/>
     </row>
     <row r="7" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="130"/>
+      <c r="A7" s="150"/>
       <c r="B7" s="87" t="s">
         <v>13</v>
       </c>
@@ -1503,7 +1503,7 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C7:G7)&amp;","</f>
         <v xml:space="preserve">    93.3589852276692, 92.7856901876314, 91.2790018368094, 77.2435690043455, 56.6416895186521,</v>
       </c>
-      <c r="K7" s="130"/>
+      <c r="K7" s="150"/>
       <c r="L7" s="87" t="s">
         <v>13</v>
       </c>
@@ -1528,8 +1528,8 @@
       </c>
     </row>
     <row r="8" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="130"/>
-      <c r="B8" s="164" t="s">
+      <c r="A8" s="150"/>
+      <c r="B8" s="120" t="s">
         <v>14</v>
       </c>
       <c r="C8" s="117">
@@ -1559,7 +1559,7 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C8:G8)&amp;","</f>
         <v xml:space="preserve">    92.7443461160275, 92.3284169124877, 91.1561086168565, 82.3077823625925, 57.6945042777187,</v>
       </c>
-      <c r="K8" s="130"/>
+      <c r="K8" s="150"/>
       <c r="L8" s="8" t="s">
         <v>14</v>
       </c>
@@ -1584,7 +1584,7 @@
       </c>
     </row>
     <row r="9" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="130"/>
+      <c r="A9" s="150"/>
       <c r="B9" s="8" t="s">
         <v>15</v>
       </c>
@@ -1612,7 +1612,7 @@
         <v>83.937535593589331</v>
       </c>
       <c r="J9" s="12"/>
-      <c r="K9" s="130"/>
+      <c r="K9" s="150"/>
       <c r="L9" s="8" t="s">
         <v>15</v>
       </c>
@@ -1634,7 +1634,7 @@
       <c r="R9" s="12"/>
     </row>
     <row r="10" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="130"/>
+      <c r="A10" s="150"/>
       <c r="B10" s="8" t="s">
         <v>18</v>
       </c>
@@ -1662,7 +1662,7 @@
         <v>83.864141342053131</v>
       </c>
       <c r="J10" s="12"/>
-      <c r="K10" s="130"/>
+      <c r="K10" s="150"/>
       <c r="L10" s="8" t="s">
         <v>18</v>
       </c>
@@ -1687,8 +1687,8 @@
       </c>
     </row>
     <row r="11" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="130"/>
-      <c r="B11" s="164" t="s">
+      <c r="A11" s="150"/>
+      <c r="B11" s="120" t="s">
         <v>25</v>
       </c>
       <c r="C11" s="117">
@@ -1715,7 +1715,7 @@
         <v>83.059021019501316</v>
       </c>
       <c r="J11" s="12"/>
-      <c r="K11" s="130"/>
+      <c r="K11" s="150"/>
       <c r="L11" s="8" t="s">
         <v>25</v>
       </c>
@@ -1737,7 +1737,7 @@
       <c r="R11" s="12"/>
     </row>
     <row r="12" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="130"/>
+      <c r="A12" s="150"/>
       <c r="B12" s="85" t="s">
         <v>16</v>
       </c>
@@ -1765,7 +1765,7 @@
         <v>79.788719066918105</v>
       </c>
       <c r="J12" s="12"/>
-      <c r="K12" s="130"/>
+      <c r="K12" s="150"/>
       <c r="L12" s="85" t="s">
         <v>16</v>
       </c>
@@ -1787,7 +1787,7 @@
       <c r="R12" s="12"/>
     </row>
     <row r="13" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="130"/>
+      <c r="A13" s="150"/>
       <c r="B13" s="85" t="s">
         <v>19</v>
       </c>
@@ -1815,7 +1815,7 @@
         <v>82.358773198009231</v>
       </c>
       <c r="J13" s="12"/>
-      <c r="K13" s="130"/>
+      <c r="K13" s="150"/>
       <c r="L13" s="85" t="s">
         <v>19</v>
       </c>
@@ -1840,7 +1840,7 @@
       </c>
     </row>
     <row r="14" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="128"/>
+      <c r="A14" s="143"/>
       <c r="B14" s="85" t="s">
         <v>26</v>
       </c>
@@ -1868,7 +1868,7 @@
         <v>80.728613659431886</v>
       </c>
       <c r="J14" s="12"/>
-      <c r="K14" s="128"/>
+      <c r="K14" s="143"/>
       <c r="L14" s="85" t="s">
         <v>26</v>
       </c>
@@ -1890,34 +1890,34 @@
       <c r="R14" s="12"/>
     </row>
     <row r="15" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="123" t="s">
+      <c r="A15" s="140" t="s">
         <v>20</v>
       </c>
-      <c r="B15" s="127"/>
-      <c r="C15" s="127"/>
-      <c r="D15" s="127"/>
-      <c r="E15" s="127"/>
-      <c r="F15" s="127"/>
-      <c r="G15" s="124"/>
+      <c r="B15" s="141"/>
+      <c r="C15" s="141"/>
+      <c r="D15" s="141"/>
+      <c r="E15" s="141"/>
+      <c r="F15" s="141"/>
+      <c r="G15" s="142"/>
       <c r="H15" s="34"/>
       <c r="I15" s="34"/>
       <c r="J15" s="12"/>
-      <c r="K15" s="123" t="s">
+      <c r="K15" s="140" t="s">
         <v>20</v>
       </c>
-      <c r="L15" s="127"/>
-      <c r="M15" s="127"/>
-      <c r="N15" s="127"/>
-      <c r="O15" s="127"/>
-      <c r="P15" s="127"/>
-      <c r="Q15" s="124"/>
+      <c r="L15" s="141"/>
+      <c r="M15" s="141"/>
+      <c r="N15" s="141"/>
+      <c r="O15" s="141"/>
+      <c r="P15" s="141"/>
+      <c r="Q15" s="142"/>
       <c r="R15" s="12"/>
     </row>
     <row r="16" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="128" t="s">
+      <c r="A16" s="143" t="s">
         <v>7</v>
       </c>
-      <c r="B16" s="129"/>
+      <c r="B16" s="144"/>
       <c r="C16" s="117">
         <v>93.207752662220258</v>
       </c>
@@ -1945,10 +1945,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C16:G16)&amp;","</f>
         <v xml:space="preserve">    93.2077526622203, 92.7830344553153, 90.5658843646283, 73.0768864782567, 58.5569944376681,</v>
       </c>
-      <c r="K16" s="128" t="s">
+      <c r="K16" s="143" t="s">
         <v>7</v>
       </c>
-      <c r="L16" s="129"/>
+      <c r="L16" s="144"/>
       <c r="M16" s="80">
         <v>4.081079160307894</v>
       </c>
@@ -1970,10 +1970,10 @@
       </c>
     </row>
     <row r="17" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="125" t="s">
+      <c r="A17" s="145" t="s">
         <v>8</v>
       </c>
-      <c r="B17" s="126"/>
+      <c r="B17" s="146"/>
       <c r="C17" s="117">
         <v>93.534975792754821</v>
       </c>
@@ -2001,10 +2001,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C17:G17)&amp;","</f>
         <v xml:space="preserve">    93.5349757927548, 92.3364677318431, 88.5935201284902, 71.0452945094681, 53.4670628638656,</v>
       </c>
-      <c r="K17" s="123" t="s">
+      <c r="K17" s="140" t="s">
         <v>8</v>
       </c>
-      <c r="L17" s="124"/>
+      <c r="L17" s="142"/>
       <c r="M17" s="80">
         <v>3.8494978151380188</v>
       </c>
@@ -2026,10 +2026,10 @@
       </c>
     </row>
     <row r="18" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="123" t="s">
+      <c r="A18" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="B18" s="124"/>
+      <c r="B18" s="142"/>
       <c r="C18" s="117">
         <v>93.005297046975599</v>
       </c>
@@ -2057,10 +2057,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C18:G18)&amp;","</f>
         <v xml:space="preserve">    93.0052970469756, 91.9024443694726, 89.1162783991788, 72.2588142342639, 53.8436289817963,</v>
       </c>
-      <c r="K18" s="123" t="s">
+      <c r="K18" s="140" t="s">
         <v>21</v>
       </c>
-      <c r="L18" s="124"/>
+      <c r="L18" s="142"/>
       <c r="M18" s="80">
         <v>3.458803648865628</v>
       </c>
@@ -2082,34 +2082,34 @@
       </c>
     </row>
     <row r="19" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="123" t="s">
+      <c r="A19" s="140" t="s">
         <v>23</v>
       </c>
-      <c r="B19" s="127"/>
-      <c r="C19" s="127"/>
-      <c r="D19" s="127"/>
-      <c r="E19" s="127"/>
-      <c r="F19" s="127"/>
-      <c r="G19" s="124"/>
+      <c r="B19" s="141"/>
+      <c r="C19" s="141"/>
+      <c r="D19" s="141"/>
+      <c r="E19" s="141"/>
+      <c r="F19" s="141"/>
+      <c r="G19" s="142"/>
       <c r="H19" s="34"/>
       <c r="I19" s="34"/>
       <c r="J19" s="12"/>
-      <c r="K19" s="123" t="s">
+      <c r="K19" s="140" t="s">
         <v>23</v>
       </c>
-      <c r="L19" s="127"/>
-      <c r="M19" s="127"/>
-      <c r="N19" s="127"/>
-      <c r="O19" s="127"/>
-      <c r="P19" s="127"/>
-      <c r="Q19" s="124"/>
+      <c r="L19" s="141"/>
+      <c r="M19" s="141"/>
+      <c r="N19" s="141"/>
+      <c r="O19" s="141"/>
+      <c r="P19" s="141"/>
+      <c r="Q19" s="142"/>
       <c r="R19" s="12"/>
     </row>
     <row r="20" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="128" t="s">
+      <c r="A20" s="143" t="s">
         <v>7</v>
       </c>
-      <c r="B20" s="129"/>
+      <c r="B20" s="144"/>
       <c r="C20" s="117">
         <v>93.204569243678591</v>
       </c>
@@ -2137,10 +2137,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C20:G20)&amp;","</f>
         <v xml:space="preserve">    93.2045692436786, 92.7189364383198, 91.0101961666335, 77.7756122457807, 55.9218563021018,</v>
       </c>
-      <c r="K20" s="128" t="s">
+      <c r="K20" s="143" t="s">
         <v>7</v>
       </c>
-      <c r="L20" s="129"/>
+      <c r="L20" s="144"/>
       <c r="M20" s="80">
         <v>3.5338969773137729</v>
       </c>
@@ -2162,10 +2162,10 @@
       </c>
     </row>
     <row r="21" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="125" t="s">
+      <c r="A21" s="145" t="s">
         <v>8</v>
       </c>
-      <c r="B21" s="126"/>
+      <c r="B21" s="146"/>
       <c r="C21" s="117">
         <v>91.935155148400952</v>
       </c>
@@ -2193,10 +2193,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C21:G21)&amp;","</f>
         <v xml:space="preserve">    91.935155148401, 91.6922551233142, 89.8476486244114, 79.4007474113098, 53.2536440626649,</v>
       </c>
-      <c r="K21" s="123" t="s">
+      <c r="K21" s="140" t="s">
         <v>8</v>
       </c>
-      <c r="L21" s="124"/>
+      <c r="L21" s="142"/>
       <c r="M21" s="80">
         <v>3.0404967647063641</v>
       </c>
@@ -2218,10 +2218,10 @@
       </c>
     </row>
     <row r="22" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="123" t="s">
+      <c r="A22" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="B22" s="124"/>
+      <c r="B22" s="142"/>
       <c r="C22" s="117">
         <v>93.32960781090955</v>
       </c>
@@ -2249,10 +2249,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C22:G22)&amp;","</f>
         <v xml:space="preserve">    93.3296078109096, 92.6274333399655, 90.919543710009, 77.7434003177651, 58.3910702803081,</v>
       </c>
-      <c r="K22" s="123" t="s">
+      <c r="K22" s="140" t="s">
         <v>21</v>
       </c>
-      <c r="L22" s="124"/>
+      <c r="L22" s="142"/>
       <c r="M22" s="80">
         <v>3.3471189071482028</v>
       </c>
@@ -2274,34 +2274,34 @@
       </c>
     </row>
     <row r="23" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="123" t="s">
+      <c r="A23" s="140" t="s">
         <v>24</v>
       </c>
-      <c r="B23" s="127"/>
-      <c r="C23" s="127"/>
-      <c r="D23" s="127"/>
-      <c r="E23" s="127"/>
-      <c r="F23" s="127"/>
-      <c r="G23" s="124"/>
+      <c r="B23" s="141"/>
+      <c r="C23" s="141"/>
+      <c r="D23" s="141"/>
+      <c r="E23" s="141"/>
+      <c r="F23" s="141"/>
+      <c r="G23" s="142"/>
       <c r="H23" s="34"/>
       <c r="I23" s="34"/>
       <c r="J23" s="12"/>
-      <c r="K23" s="123" t="s">
+      <c r="K23" s="140" t="s">
         <v>23</v>
       </c>
-      <c r="L23" s="127"/>
-      <c r="M23" s="127"/>
-      <c r="N23" s="127"/>
-      <c r="O23" s="127"/>
-      <c r="P23" s="127"/>
-      <c r="Q23" s="124"/>
+      <c r="L23" s="141"/>
+      <c r="M23" s="141"/>
+      <c r="N23" s="141"/>
+      <c r="O23" s="141"/>
+      <c r="P23" s="141"/>
+      <c r="Q23" s="142"/>
       <c r="R23" s="12"/>
     </row>
     <row r="24" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="128" t="s">
+      <c r="A24" s="143" t="s">
         <v>7</v>
       </c>
-      <c r="B24" s="129"/>
+      <c r="B24" s="144"/>
       <c r="C24">
         <v>92.975423662834444</v>
       </c>
@@ -2329,10 +2329,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C24:G24)&amp;","</f>
         <v xml:space="preserve">    92.9754236628344, 92.0442477876106, 90.1622505384995, 76.3966873992566, 53.4792890365257,</v>
       </c>
-      <c r="K24" s="128" t="s">
+      <c r="K24" s="143" t="s">
         <v>7</v>
       </c>
-      <c r="L24" s="129"/>
+      <c r="L24" s="144"/>
       <c r="M24">
         <v>3.5495358905530332</v>
       </c>
@@ -2354,10 +2354,10 @@
       </c>
     </row>
     <row r="25" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="125" t="s">
+      <c r="A25" s="145" t="s">
         <v>8</v>
       </c>
-      <c r="B25" s="126"/>
+      <c r="B25" s="146"/>
       <c r="C25">
         <v>89.994106062047834</v>
       </c>
@@ -2385,10 +2385,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C25:G25)&amp;","</f>
         <v xml:space="preserve">    89.9941060620478, 88.8721730580138, 88.0729677592367, 74.3787864370222, 49.9763117904711,</v>
       </c>
-      <c r="K25" s="123" t="s">
+      <c r="K25" s="140" t="s">
         <v>8</v>
       </c>
-      <c r="L25" s="124"/>
+      <c r="L25" s="142"/>
       <c r="M25">
         <v>2.7058137956739952</v>
       </c>
@@ -2410,10 +2410,10 @@
       </c>
     </row>
     <row r="26" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="123" t="s">
+      <c r="A26" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="B26" s="124"/>
+      <c r="B26" s="142"/>
       <c r="C26">
         <v>93.745335167259228</v>
       </c>
@@ -2441,10 +2441,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C26:G26)&amp;","</f>
         <v xml:space="preserve">    93.7453351672592, 92.527080684089, 90.7286251034467, 73.3969180817596, 55.8694942574474,</v>
       </c>
-      <c r="K26" s="123" t="s">
+      <c r="K26" s="140" t="s">
         <v>21</v>
       </c>
-      <c r="L26" s="124"/>
+      <c r="L26" s="142"/>
       <c r="M26">
         <v>3.2813687789549171</v>
       </c>
@@ -2532,10 +2532,10 @@
       <c r="R28" s="1"/>
     </row>
     <row r="29" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="131" t="s">
+      <c r="A29" s="134" t="s">
         <v>5</v>
       </c>
-      <c r="B29" s="132"/>
+      <c r="B29" s="135"/>
       <c r="C29" s="77">
         <v>92.485449200300948</v>
       </c>
@@ -2557,10 +2557,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C29:G29)&amp;","</f>
         <v xml:space="preserve">    92.4854492003009, 92.1853579700095, 90.0493612740203, 76.4241798948027, 55.8171663737853,</v>
       </c>
-      <c r="K29" s="131" t="s">
+      <c r="K29" s="134" t="s">
         <v>5</v>
       </c>
-      <c r="L29" s="132"/>
+      <c r="L29" s="135"/>
       <c r="M29" s="77">
         <v>4.0542209595909764</v>
       </c>
@@ -2582,10 +2582,10 @@
       </c>
     </row>
     <row r="30" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="131" t="s">
+      <c r="A30" s="134" t="s">
         <v>6</v>
       </c>
-      <c r="B30" s="132"/>
+      <c r="B30" s="135"/>
       <c r="C30" s="80">
         <v>93.221737995090834</v>
       </c>
@@ -2607,10 +2607,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C30:G30)&amp;","</f>
         <v xml:space="preserve">    93.2217379950908, 91.8880330056846, 90.0239389840154, 72.2904200814482, 51.8413052641743,</v>
       </c>
-      <c r="K30" s="131" t="s">
+      <c r="K30" s="134" t="s">
         <v>6</v>
       </c>
-      <c r="L30" s="132"/>
+      <c r="L30" s="135"/>
       <c r="M30" s="80">
         <v>3.877808098377264</v>
       </c>
@@ -2632,10 +2632,10 @@
       </c>
     </row>
     <row r="31" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="133" t="s">
+      <c r="A31" s="132" t="s">
         <v>10</v>
       </c>
-      <c r="B31" s="134"/>
+      <c r="B31" s="133"/>
       <c r="C31" s="82">
         <v>88.242190127710941</v>
       </c>
@@ -2657,10 +2657,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C31:G31)&amp;","</f>
         <v xml:space="preserve">    88.2421901277109, 87.2356592457238, 86.8403563631381, 74.5410000823158, 48.9795299923061,</v>
       </c>
-      <c r="K31" s="133" t="s">
+      <c r="K31" s="132" t="s">
         <v>10</v>
       </c>
-      <c r="L31" s="134"/>
+      <c r="L31" s="133"/>
       <c r="M31" s="82">
         <v>3.345739818904093</v>
       </c>
@@ -2682,31 +2682,31 @@
       </c>
     </row>
     <row r="32" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="131" t="s">
+      <c r="A32" s="134" t="s">
         <v>12</v>
       </c>
-      <c r="B32" s="132"/>
-      <c r="C32" s="134"/>
-      <c r="D32" s="134"/>
-      <c r="E32" s="134"/>
-      <c r="F32" s="134"/>
-      <c r="G32" s="135"/>
+      <c r="B32" s="135"/>
+      <c r="C32" s="133"/>
+      <c r="D32" s="133"/>
+      <c r="E32" s="133"/>
+      <c r="F32" s="133"/>
+      <c r="G32" s="139"/>
       <c r="H32" s="38"/>
       <c r="I32" s="38"/>
       <c r="J32" s="1"/>
-      <c r="K32" s="131" t="s">
+      <c r="K32" s="134" t="s">
         <v>12</v>
       </c>
-      <c r="L32" s="132"/>
-      <c r="M32" s="134"/>
-      <c r="N32" s="134"/>
-      <c r="O32" s="134"/>
-      <c r="P32" s="134"/>
-      <c r="Q32" s="135"/>
+      <c r="L32" s="135"/>
+      <c r="M32" s="133"/>
+      <c r="N32" s="133"/>
+      <c r="O32" s="133"/>
+      <c r="P32" s="133"/>
+      <c r="Q32" s="139"/>
       <c r="R32" s="1"/>
     </row>
     <row r="33" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="120" t="s">
+      <c r="A33" s="147" t="s">
         <v>11</v>
       </c>
       <c r="B33" s="76" t="s">
@@ -2730,7 +2730,7 @@
       <c r="H33" s="38"/>
       <c r="I33" s="38"/>
       <c r="J33" s="1"/>
-      <c r="K33" s="120" t="s">
+      <c r="K33" s="147" t="s">
         <v>11</v>
       </c>
       <c r="L33" s="76" t="s">
@@ -2754,7 +2754,7 @@
       <c r="R33" s="1"/>
     </row>
     <row r="34" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="121"/>
+      <c r="A34" s="148"/>
       <c r="B34" s="86" t="s">
         <v>13</v>
       </c>
@@ -2779,7 +2779,7 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C34:G34)&amp;","</f>
         <v xml:space="preserve">    92.8847571868149, 92.3354362154591, 90.9231205519105, 76.8647908062627, 54.7003900365723,</v>
       </c>
-      <c r="K34" s="121"/>
+      <c r="K34" s="148"/>
       <c r="L34" s="86" t="s">
         <v>13</v>
       </c>
@@ -2804,7 +2804,7 @@
       </c>
     </row>
     <row r="35" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="121"/>
+      <c r="A35" s="148"/>
       <c r="B35" s="76" t="s">
         <v>14</v>
       </c>
@@ -2829,7 +2829,7 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C35:G35)&amp;","</f>
         <v xml:space="preserve">    92.3286839002613, 92.0520391167916, 90.7229467757102, 81.998727124399, 56.9326510647426,</v>
       </c>
-      <c r="K35" s="121"/>
+      <c r="K35" s="148"/>
       <c r="L35" s="76" t="s">
         <v>14</v>
       </c>
@@ -2854,7 +2854,7 @@
       </c>
     </row>
     <row r="36" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="121"/>
+      <c r="A36" s="148"/>
       <c r="B36" s="76" t="s">
         <v>15</v>
       </c>
@@ -2876,7 +2876,7 @@
       <c r="H36" s="38"/>
       <c r="I36" s="38"/>
       <c r="J36" s="1"/>
-      <c r="K36" s="121"/>
+      <c r="K36" s="148"/>
       <c r="L36" s="76" t="s">
         <v>15</v>
       </c>
@@ -2898,7 +2898,7 @@
       <c r="R36" s="1"/>
     </row>
     <row r="37" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="121"/>
+      <c r="A37" s="148"/>
       <c r="B37" s="76" t="s">
         <v>18</v>
       </c>
@@ -2920,7 +2920,7 @@
       <c r="H37" s="38"/>
       <c r="I37" s="38"/>
       <c r="J37" s="1"/>
-      <c r="K37" s="121"/>
+      <c r="K37" s="148"/>
       <c r="L37" s="76" t="s">
         <v>18</v>
       </c>
@@ -2942,7 +2942,7 @@
       <c r="R37" s="1"/>
     </row>
     <row r="38" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="121"/>
+      <c r="A38" s="148"/>
       <c r="B38" s="76" t="s">
         <v>25</v>
       </c>
@@ -2964,7 +2964,7 @@
       <c r="H38" s="38"/>
       <c r="I38" s="38"/>
       <c r="J38" s="1"/>
-      <c r="K38" s="121"/>
+      <c r="K38" s="148"/>
       <c r="L38" s="76" t="s">
         <v>25</v>
       </c>
@@ -2986,7 +2986,7 @@
       <c r="R38" s="1"/>
     </row>
     <row r="39" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="121"/>
+      <c r="A39" s="148"/>
       <c r="B39" s="76" t="s">
         <v>16</v>
       </c>
@@ -3008,7 +3008,7 @@
       <c r="H39" s="38"/>
       <c r="I39" s="38"/>
       <c r="J39" s="1"/>
-      <c r="K39" s="121"/>
+      <c r="K39" s="148"/>
       <c r="L39" s="76" t="s">
         <v>16</v>
       </c>
@@ -3030,7 +3030,7 @@
       <c r="R39" s="1"/>
     </row>
     <row r="40" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="121"/>
+      <c r="A40" s="148"/>
       <c r="B40" s="76" t="s">
         <v>19</v>
       </c>
@@ -3052,7 +3052,7 @@
       <c r="H40" s="38"/>
       <c r="I40" s="38"/>
       <c r="J40" s="1"/>
-      <c r="K40" s="121"/>
+      <c r="K40" s="148"/>
       <c r="L40" s="76" t="s">
         <v>19</v>
       </c>
@@ -3074,7 +3074,7 @@
       <c r="R40" s="1"/>
     </row>
     <row r="41" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="122"/>
+      <c r="A41" s="149"/>
       <c r="B41" s="76" t="s">
         <v>26</v>
       </c>
@@ -3096,7 +3096,7 @@
       <c r="H41" s="38"/>
       <c r="I41" s="38"/>
       <c r="J41" s="1"/>
-      <c r="K41" s="122"/>
+      <c r="K41" s="149"/>
       <c r="L41" s="76" t="s">
         <v>26</v>
       </c>
@@ -3118,34 +3118,34 @@
       <c r="R41" s="1"/>
     </row>
     <row r="42" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="131" t="s">
+      <c r="A42" s="134" t="s">
         <v>20</v>
       </c>
-      <c r="B42" s="132"/>
-      <c r="C42" s="136"/>
-      <c r="D42" s="136"/>
-      <c r="E42" s="136"/>
-      <c r="F42" s="136"/>
-      <c r="G42" s="136"/>
+      <c r="B42" s="135"/>
+      <c r="C42" s="137"/>
+      <c r="D42" s="137"/>
+      <c r="E42" s="137"/>
+      <c r="F42" s="137"/>
+      <c r="G42" s="137"/>
       <c r="H42" s="38"/>
       <c r="I42" s="38"/>
       <c r="J42" s="1"/>
-      <c r="K42" s="131" t="s">
+      <c r="K42" s="134" t="s">
         <v>20</v>
       </c>
-      <c r="L42" s="132"/>
-      <c r="M42" s="137"/>
-      <c r="N42" s="137"/>
-      <c r="O42" s="137"/>
-      <c r="P42" s="137"/>
+      <c r="L42" s="135"/>
+      <c r="M42" s="131"/>
+      <c r="N42" s="131"/>
+      <c r="O42" s="131"/>
+      <c r="P42" s="131"/>
       <c r="Q42" s="138"/>
       <c r="R42" s="1"/>
     </row>
     <row r="43" spans="1:18" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="131" t="s">
+      <c r="A43" s="134" t="s">
         <v>7</v>
       </c>
-      <c r="B43" s="132"/>
+      <c r="B43" s="135"/>
       <c r="C43" s="77">
         <v>92.781043798288394</v>
       </c>
@@ -3167,10 +3167,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C43:G43)&amp;","</f>
         <v xml:space="preserve">    92.7810437982884, 92.3938056553932, 90.0090839662476, 72.4981719652037, 56.6748529979919,</v>
       </c>
-      <c r="K43" s="139" t="s">
+      <c r="K43" s="130" t="s">
         <v>7</v>
       </c>
-      <c r="L43" s="137"/>
+      <c r="L43" s="131"/>
       <c r="M43" s="77">
         <v>4.5014366094349993</v>
       </c>
@@ -3192,10 +3192,10 @@
       </c>
     </row>
     <row r="44" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="131" t="s">
+      <c r="A44" s="134" t="s">
         <v>8</v>
       </c>
-      <c r="B44" s="132"/>
+      <c r="B44" s="135"/>
       <c r="C44" s="80">
         <v>93.113144022293241</v>
       </c>
@@ -3217,10 +3217,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C44:G44)&amp;","</f>
         <v xml:space="preserve">    93.1131440222932, 91.9496041120699, 88.043149271791, 70.4378143831585, 50.0271657882747,</v>
       </c>
-      <c r="K44" s="131" t="s">
+      <c r="K44" s="134" t="s">
         <v>8</v>
       </c>
-      <c r="L44" s="132"/>
+      <c r="L44" s="135"/>
       <c r="M44" s="80">
         <v>4.249709534316878</v>
       </c>
@@ -3242,10 +3242,10 @@
       </c>
     </row>
     <row r="45" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="131" t="s">
+      <c r="A45" s="134" t="s">
         <v>21</v>
       </c>
-      <c r="B45" s="132"/>
+      <c r="B45" s="135"/>
       <c r="C45" s="82">
         <v>92.587964837227005</v>
       </c>
@@ -3267,10 +3267,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C45:G45)&amp;","</f>
         <v xml:space="preserve">    92.587964837227, 91.4235824416001, 88.5454649294227, 71.6598005950386, 50.2664690265607,</v>
       </c>
-      <c r="K45" s="131" t="s">
+      <c r="K45" s="134" t="s">
         <v>21</v>
       </c>
-      <c r="L45" s="132"/>
+      <c r="L45" s="135"/>
       <c r="M45" s="80">
         <v>3.7645606938355249</v>
       </c>
@@ -3292,34 +3292,34 @@
       </c>
     </row>
     <row r="46" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="131" t="s">
+      <c r="A46" s="134" t="s">
         <v>23</v>
       </c>
-      <c r="B46" s="132"/>
-      <c r="C46" s="132"/>
-      <c r="D46" s="132"/>
-      <c r="E46" s="132"/>
-      <c r="F46" s="132"/>
-      <c r="G46" s="140"/>
+      <c r="B46" s="135"/>
+      <c r="C46" s="135"/>
+      <c r="D46" s="135"/>
+      <c r="E46" s="135"/>
+      <c r="F46" s="135"/>
+      <c r="G46" s="136"/>
       <c r="H46" s="38"/>
       <c r="I46" s="38"/>
       <c r="J46" s="1"/>
-      <c r="K46" s="131" t="s">
+      <c r="K46" s="134" t="s">
         <v>23</v>
       </c>
-      <c r="L46" s="132"/>
-      <c r="M46" s="132"/>
-      <c r="N46" s="132"/>
-      <c r="O46" s="132"/>
-      <c r="P46" s="132"/>
-      <c r="Q46" s="140"/>
+      <c r="L46" s="135"/>
+      <c r="M46" s="135"/>
+      <c r="N46" s="135"/>
+      <c r="O46" s="135"/>
+      <c r="P46" s="135"/>
+      <c r="Q46" s="136"/>
       <c r="R46" s="1"/>
     </row>
     <row r="47" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="139" t="s">
+      <c r="A47" s="130" t="s">
         <v>7</v>
       </c>
-      <c r="B47" s="137"/>
+      <c r="B47" s="131"/>
       <c r="C47" s="77">
         <v>92.779242983398433</v>
       </c>
@@ -3341,10 +3341,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C47:G47)&amp;","</f>
         <v xml:space="preserve">    92.7792429833984, 92.2402701949049, 90.5523014335592, 77.4468153062754, 54.049481297537,</v>
       </c>
-      <c r="K47" s="139" t="s">
+      <c r="K47" s="130" t="s">
         <v>7</v>
       </c>
-      <c r="L47" s="137"/>
+      <c r="L47" s="131"/>
       <c r="M47" s="77">
         <v>3.8708284466838099</v>
       </c>
@@ -3366,10 +3366,10 @@
       </c>
     </row>
     <row r="48" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="133" t="s">
+      <c r="A48" s="132" t="s">
         <v>8</v>
       </c>
-      <c r="B48" s="134"/>
+      <c r="B48" s="133"/>
       <c r="C48" s="80">
         <v>91.529115829853595</v>
       </c>
@@ -3391,10 +3391,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C48:G48)&amp;","</f>
         <v xml:space="preserve">    91.5291158298536, 91.3506434233222, 89.3417609327998, 79.0450519987888, 52.3197117316979,</v>
       </c>
-      <c r="K48" s="131" t="s">
+      <c r="K48" s="134" t="s">
         <v>8</v>
       </c>
-      <c r="L48" s="132"/>
+      <c r="L48" s="135"/>
       <c r="M48" s="80">
         <v>3.326792742141544</v>
       </c>
@@ -3416,10 +3416,10 @@
       </c>
     </row>
     <row r="49" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="131" t="s">
+      <c r="A49" s="134" t="s">
         <v>21</v>
       </c>
-      <c r="B49" s="132"/>
+      <c r="B49" s="135"/>
       <c r="C49" s="80">
         <v>92.904210456970588</v>
       </c>
@@ -3441,10 +3441,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C49:G49)&amp;","</f>
         <v xml:space="preserve">    92.9042104569706, 92.1891124359732, 90.4960366989424, 77.336951327755, 56.2225359371609,</v>
       </c>
-      <c r="K49" s="131" t="s">
+      <c r="K49" s="134" t="s">
         <v>21</v>
       </c>
-      <c r="L49" s="132"/>
+      <c r="L49" s="135"/>
       <c r="M49" s="80">
         <v>3.6016716439248402</v>
       </c>
@@ -3466,34 +3466,34 @@
       </c>
     </row>
     <row r="50" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="131" t="s">
+      <c r="A50" s="134" t="s">
         <v>24</v>
       </c>
-      <c r="B50" s="132"/>
-      <c r="C50" s="132"/>
-      <c r="D50" s="132"/>
-      <c r="E50" s="132"/>
-      <c r="F50" s="132"/>
-      <c r="G50" s="140"/>
+      <c r="B50" s="135"/>
+      <c r="C50" s="135"/>
+      <c r="D50" s="135"/>
+      <c r="E50" s="135"/>
+      <c r="F50" s="135"/>
+      <c r="G50" s="136"/>
       <c r="H50" s="38"/>
       <c r="I50" s="38"/>
       <c r="J50" s="1"/>
-      <c r="K50" s="131" t="s">
+      <c r="K50" s="134" t="s">
         <v>24</v>
       </c>
-      <c r="L50" s="132"/>
-      <c r="M50" s="132"/>
-      <c r="N50" s="132"/>
-      <c r="O50" s="132"/>
-      <c r="P50" s="132"/>
-      <c r="Q50" s="140"/>
+      <c r="L50" s="135"/>
+      <c r="M50" s="135"/>
+      <c r="N50" s="135"/>
+      <c r="O50" s="135"/>
+      <c r="P50" s="135"/>
+      <c r="Q50" s="136"/>
       <c r="R50" s="1"/>
     </row>
     <row r="51" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="139" t="s">
+      <c r="A51" s="130" t="s">
         <v>7</v>
       </c>
-      <c r="B51" s="137"/>
+      <c r="B51" s="131"/>
       <c r="C51">
         <v>92.570848555845046</v>
       </c>
@@ -3515,10 +3515,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C51:G51)&amp;","</f>
         <v xml:space="preserve">    92.570848555845, 91.6300540976163, 89.7927570734142, 76.1721413690566, 51.9263065801623,</v>
       </c>
-      <c r="K51" s="139" t="s">
+      <c r="K51" s="130" t="s">
         <v>7</v>
       </c>
-      <c r="L51" s="137"/>
+      <c r="L51" s="131"/>
       <c r="M51">
         <v>3.9499959320021021</v>
       </c>
@@ -3540,10 +3540,10 @@
       </c>
     </row>
     <row r="52" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="133" t="s">
+      <c r="A52" s="132" t="s">
         <v>8</v>
       </c>
-      <c r="B52" s="134"/>
+      <c r="B52" s="133"/>
       <c r="C52">
         <v>89.680415246872897</v>
       </c>
@@ -3565,10 +3565,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C52:G52)&amp;","</f>
         <v xml:space="preserve">    89.6804152468729, 88.4223455285604, 87.8396293056582, 74.0723408331451, 48.7869620248166,</v>
       </c>
-      <c r="K52" s="131" t="s">
+      <c r="K52" s="134" t="s">
         <v>8</v>
       </c>
-      <c r="L52" s="132"/>
+      <c r="L52" s="135"/>
       <c r="M52">
         <v>2.856200195635104</v>
       </c>
@@ -3590,10 +3590,10 @@
       </c>
     </row>
     <row r="53" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="131" t="s">
+      <c r="A53" s="134" t="s">
         <v>21</v>
       </c>
-      <c r="B53" s="132"/>
+      <c r="B53" s="135"/>
       <c r="C53">
         <v>93.356158779022067</v>
       </c>
@@ -3615,10 +3615,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C53:G53)&amp;","</f>
         <v xml:space="preserve">    93.3561587790221, 92.0903349534992, 90.2830615749057, 73.0070478965122, 53.7670892090723,</v>
       </c>
-      <c r="K53" s="131" t="s">
+      <c r="K53" s="134" t="s">
         <v>21</v>
       </c>
-      <c r="L53" s="132"/>
+      <c r="L53" s="135"/>
       <c r="M53">
         <v>3.7078351435189272</v>
       </c>
@@ -3665,58 +3665,6 @@
     </row>
   </sheetData>
   <mergeCells count="68">
-    <mergeCell ref="A51:B51"/>
-    <mergeCell ref="K51:L51"/>
-    <mergeCell ref="A52:B52"/>
-    <mergeCell ref="K52:L52"/>
-    <mergeCell ref="A53:B53"/>
-    <mergeCell ref="K53:L53"/>
-    <mergeCell ref="A47:B47"/>
-    <mergeCell ref="K47:L47"/>
-    <mergeCell ref="A48:B48"/>
-    <mergeCell ref="K48:L48"/>
-    <mergeCell ref="A49:B49"/>
-    <mergeCell ref="K49:L49"/>
-    <mergeCell ref="A50:G50"/>
-    <mergeCell ref="K50:Q50"/>
-    <mergeCell ref="A45:B45"/>
-    <mergeCell ref="K45:L45"/>
-    <mergeCell ref="A46:G46"/>
-    <mergeCell ref="K46:Q46"/>
-    <mergeCell ref="A42:G42"/>
-    <mergeCell ref="K42:Q42"/>
-    <mergeCell ref="A43:B43"/>
-    <mergeCell ref="K43:L43"/>
-    <mergeCell ref="A44:B44"/>
-    <mergeCell ref="K44:L44"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="K30:L30"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="K31:L31"/>
-    <mergeCell ref="A32:G32"/>
-    <mergeCell ref="K32:Q32"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="K29:L29"/>
-    <mergeCell ref="A23:G23"/>
-    <mergeCell ref="K23:Q23"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="K24:L24"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="K25:L25"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="K26:L26"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="K20:L20"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="K21:L21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="K22:L22"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="K17:L17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="K18:L18"/>
-    <mergeCell ref="A19:G19"/>
-    <mergeCell ref="K19:Q19"/>
     <mergeCell ref="A33:A41"/>
     <mergeCell ref="K33:K41"/>
     <mergeCell ref="A2:B2"/>
@@ -3733,6 +3681,58 @@
     <mergeCell ref="K16:L16"/>
     <mergeCell ref="A6:A14"/>
     <mergeCell ref="K6:K14"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="K17:L17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="K18:L18"/>
+    <mergeCell ref="A19:G19"/>
+    <mergeCell ref="K19:Q19"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="K20:L20"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="K21:L21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="K22:L22"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="K29:L29"/>
+    <mergeCell ref="A23:G23"/>
+    <mergeCell ref="K23:Q23"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="K24:L24"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="K25:L25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="K26:L26"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="K30:L30"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="K31:L31"/>
+    <mergeCell ref="A32:G32"/>
+    <mergeCell ref="K32:Q32"/>
+    <mergeCell ref="A42:G42"/>
+    <mergeCell ref="K42:Q42"/>
+    <mergeCell ref="A43:B43"/>
+    <mergeCell ref="K43:L43"/>
+    <mergeCell ref="A44:B44"/>
+    <mergeCell ref="K44:L44"/>
+    <mergeCell ref="A50:G50"/>
+    <mergeCell ref="K50:Q50"/>
+    <mergeCell ref="A45:B45"/>
+    <mergeCell ref="K45:L45"/>
+    <mergeCell ref="A46:G46"/>
+    <mergeCell ref="K46:Q46"/>
+    <mergeCell ref="A47:B47"/>
+    <mergeCell ref="K47:L47"/>
+    <mergeCell ref="A48:B48"/>
+    <mergeCell ref="K48:L48"/>
+    <mergeCell ref="A49:B49"/>
+    <mergeCell ref="K49:L49"/>
+    <mergeCell ref="A51:B51"/>
+    <mergeCell ref="K51:L51"/>
+    <mergeCell ref="A52:B52"/>
+    <mergeCell ref="K52:L52"/>
+    <mergeCell ref="A53:B53"/>
+    <mergeCell ref="K53:L53"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C2:C4 C6:C14">
@@ -3888,17 +3888,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C8:G14">
+    <cfRule type="colorScale" priority="321">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="320">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="321">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -4034,6 +4034,16 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C24:G26">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="min"/>
@@ -4055,16 +4065,6 @@
       </colorScale>
     </cfRule>
     <cfRule type="colorScale" priority="7">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -4135,40 +4135,40 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="H46:H53">
+    <cfRule type="colorScale" priority="401">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="402">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="403">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="I2:I26">
     <cfRule type="colorScale" priority="1">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H46:H53">
-    <cfRule type="colorScale" priority="401">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="402">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="403">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -4304,10 +4304,10 @@
       <c r="V1" s="12"/>
     </row>
     <row r="2" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="123" t="s">
+      <c r="A2" s="140" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="124"/>
+      <c r="B2" s="142"/>
       <c r="C2" s="20"/>
       <c r="D2" s="21"/>
       <c r="E2" s="21"/>
@@ -4327,10 +4327,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C2:I2)&amp;","</f>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M2" s="123" t="s">
+      <c r="M2" s="140" t="s">
         <v>5</v>
       </c>
-      <c r="N2" s="124"/>
+      <c r="N2" s="142"/>
       <c r="O2" s="31"/>
       <c r="P2" s="32"/>
       <c r="Q2" s="32"/>
@@ -4344,10 +4344,10 @@
       </c>
     </row>
     <row r="3" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="123" t="s">
+      <c r="A3" s="140" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="124"/>
+      <c r="B3" s="142"/>
       <c r="C3" s="31"/>
       <c r="D3" s="32"/>
       <c r="E3" s="32"/>
@@ -4367,10 +4367,10 @@
         <f t="shared" ref="L3:L18" si="0">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C3:I3)&amp;","</f>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M3" s="123" t="s">
+      <c r="M3" s="140" t="s">
         <v>6</v>
       </c>
-      <c r="N3" s="124"/>
+      <c r="N3" s="142"/>
       <c r="O3" s="31"/>
       <c r="P3" s="32"/>
       <c r="Q3" s="32"/>
@@ -4384,10 +4384,10 @@
       </c>
     </row>
     <row r="4" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="123" t="s">
+      <c r="A4" s="140" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="124"/>
+      <c r="B4" s="142"/>
       <c r="C4" s="24"/>
       <c r="D4" s="26"/>
       <c r="E4" s="26"/>
@@ -4407,10 +4407,10 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M4" s="123" t="s">
+      <c r="M4" s="140" t="s">
         <v>10</v>
       </c>
-      <c r="N4" s="124"/>
+      <c r="N4" s="142"/>
       <c r="O4" s="39"/>
       <c r="P4" s="26"/>
       <c r="Q4" s="26"/>
@@ -4424,35 +4424,35 @@
       </c>
     </row>
     <row r="5" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="123" t="s">
+      <c r="A5" s="140" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="127"/>
-      <c r="C5" s="127"/>
-      <c r="D5" s="127"/>
-      <c r="E5" s="127"/>
-      <c r="F5" s="127"/>
-      <c r="G5" s="127"/>
-      <c r="H5" s="127"/>
-      <c r="I5" s="124"/>
+      <c r="B5" s="141"/>
+      <c r="C5" s="141"/>
+      <c r="D5" s="141"/>
+      <c r="E5" s="141"/>
+      <c r="F5" s="141"/>
+      <c r="G5" s="141"/>
+      <c r="H5" s="141"/>
+      <c r="I5" s="142"/>
       <c r="J5" s="34"/>
       <c r="K5" s="34"/>
       <c r="L5" s="12"/>
-      <c r="M5" s="123" t="s">
+      <c r="M5" s="140" t="s">
         <v>12</v>
       </c>
-      <c r="N5" s="127"/>
-      <c r="O5" s="127"/>
-      <c r="P5" s="127"/>
-      <c r="Q5" s="127"/>
-      <c r="R5" s="127"/>
-      <c r="S5" s="127"/>
-      <c r="T5" s="127"/>
-      <c r="U5" s="124"/>
+      <c r="N5" s="141"/>
+      <c r="O5" s="141"/>
+      <c r="P5" s="141"/>
+      <c r="Q5" s="141"/>
+      <c r="R5" s="141"/>
+      <c r="S5" s="141"/>
+      <c r="T5" s="141"/>
+      <c r="U5" s="142"/>
       <c r="V5" s="12"/>
     </row>
     <row r="6" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="125" t="s">
+      <c r="A6" s="145" t="s">
         <v>11</v>
       </c>
       <c r="B6" s="8" t="s">
@@ -4477,7 +4477,7 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M6" s="125" t="s">
+      <c r="M6" s="145" t="s">
         <v>11</v>
       </c>
       <c r="N6" s="8" t="s">
@@ -4496,7 +4496,7 @@
       </c>
     </row>
     <row r="7" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="130"/>
+      <c r="A7" s="150"/>
       <c r="B7" s="8" t="s">
         <v>14</v>
       </c>
@@ -4519,7 +4519,7 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M7" s="130"/>
+      <c r="M7" s="150"/>
       <c r="N7" s="8" t="s">
         <v>14</v>
       </c>
@@ -4536,7 +4536,7 @@
       </c>
     </row>
     <row r="8" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="130"/>
+      <c r="A8" s="150"/>
       <c r="B8" s="8" t="s">
         <v>17</v>
       </c>
@@ -4559,7 +4559,7 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M8" s="130"/>
+      <c r="M8" s="150"/>
       <c r="N8" s="8" t="s">
         <v>17</v>
       </c>
@@ -4573,7 +4573,7 @@
       <c r="V8" s="12"/>
     </row>
     <row r="9" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="130"/>
+      <c r="A9" s="150"/>
       <c r="B9" s="8" t="s">
         <v>18</v>
       </c>
@@ -4596,7 +4596,7 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M9" s="130"/>
+      <c r="M9" s="150"/>
       <c r="N9" s="8" t="s">
         <v>18</v>
       </c>
@@ -4610,7 +4610,7 @@
       <c r="V9" s="12"/>
     </row>
     <row r="10" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="130"/>
+      <c r="A10" s="150"/>
       <c r="B10" s="8" t="s">
         <v>15</v>
       </c>
@@ -4633,7 +4633,7 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M10" s="130"/>
+      <c r="M10" s="150"/>
       <c r="N10" s="8" t="s">
         <v>15</v>
       </c>
@@ -4647,7 +4647,7 @@
       <c r="V10" s="12"/>
     </row>
     <row r="11" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="130"/>
+      <c r="A11" s="150"/>
       <c r="B11" s="8" t="s">
         <v>25</v>
       </c>
@@ -4670,7 +4670,7 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M11" s="130"/>
+      <c r="M11" s="150"/>
       <c r="N11" s="8" t="s">
         <v>25</v>
       </c>
@@ -4684,7 +4684,7 @@
       <c r="V11" s="12"/>
     </row>
     <row r="12" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="130"/>
+      <c r="A12" s="150"/>
       <c r="B12" s="8" t="s">
         <v>19</v>
       </c>
@@ -4707,7 +4707,7 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M12" s="130"/>
+      <c r="M12" s="150"/>
       <c r="N12" s="8" t="s">
         <v>19</v>
       </c>
@@ -4721,7 +4721,7 @@
       <c r="V12" s="12"/>
     </row>
     <row r="13" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="130"/>
+      <c r="A13" s="150"/>
       <c r="B13" s="8" t="s">
         <v>16</v>
       </c>
@@ -4744,7 +4744,7 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M13" s="130"/>
+      <c r="M13" s="150"/>
       <c r="N13" s="8" t="s">
         <v>16</v>
       </c>
@@ -4758,7 +4758,7 @@
       <c r="V13" s="12"/>
     </row>
     <row r="14" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="128"/>
+      <c r="A14" s="143"/>
       <c r="B14" s="8" t="s">
         <v>26</v>
       </c>
@@ -4781,7 +4781,7 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M14" s="128"/>
+      <c r="M14" s="143"/>
       <c r="N14" s="8" t="s">
         <v>26</v>
       </c>
@@ -4795,38 +4795,38 @@
       <c r="V14" s="12"/>
     </row>
     <row r="15" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="123" t="s">
+      <c r="A15" s="140" t="s">
         <v>20</v>
       </c>
-      <c r="B15" s="127"/>
-      <c r="C15" s="141"/>
-      <c r="D15" s="141"/>
-      <c r="E15" s="141"/>
-      <c r="F15" s="141"/>
-      <c r="G15" s="141"/>
-      <c r="H15" s="141"/>
-      <c r="I15" s="142"/>
+      <c r="B15" s="141"/>
+      <c r="C15" s="153"/>
+      <c r="D15" s="153"/>
+      <c r="E15" s="153"/>
+      <c r="F15" s="153"/>
+      <c r="G15" s="153"/>
+      <c r="H15" s="153"/>
+      <c r="I15" s="154"/>
       <c r="J15" s="34"/>
       <c r="K15" s="34"/>
       <c r="L15" s="12"/>
-      <c r="M15" s="123" t="s">
+      <c r="M15" s="140" t="s">
         <v>20</v>
       </c>
-      <c r="N15" s="127"/>
-      <c r="O15" s="144"/>
-      <c r="P15" s="144"/>
-      <c r="Q15" s="144"/>
-      <c r="R15" s="144"/>
-      <c r="S15" s="144"/>
-      <c r="T15" s="144"/>
-      <c r="U15" s="126"/>
+      <c r="N15" s="141"/>
+      <c r="O15" s="155"/>
+      <c r="P15" s="155"/>
+      <c r="Q15" s="155"/>
+      <c r="R15" s="155"/>
+      <c r="S15" s="155"/>
+      <c r="T15" s="155"/>
+      <c r="U15" s="146"/>
       <c r="V15" s="12"/>
     </row>
     <row r="16" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="123" t="s">
+      <c r="A16" s="140" t="s">
         <v>7</v>
       </c>
-      <c r="B16" s="124"/>
+      <c r="B16" s="142"/>
       <c r="C16" s="42"/>
       <c r="D16" s="43"/>
       <c r="E16" s="43"/>
@@ -4846,10 +4846,10 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M16" s="123" t="s">
+      <c r="M16" s="140" t="s">
         <v>7</v>
       </c>
-      <c r="N16" s="124"/>
+      <c r="N16" s="142"/>
       <c r="O16" s="42"/>
       <c r="P16" s="43"/>
       <c r="Q16" s="43"/>
@@ -4863,10 +4863,10 @@
       </c>
     </row>
     <row r="17" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="125" t="s">
+      <c r="A17" s="145" t="s">
         <v>8</v>
       </c>
-      <c r="B17" s="126"/>
+      <c r="B17" s="146"/>
       <c r="C17" s="45"/>
       <c r="D17" s="12"/>
       <c r="E17" s="12"/>
@@ -4886,10 +4886,10 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M17" s="123" t="s">
+      <c r="M17" s="140" t="s">
         <v>8</v>
       </c>
-      <c r="N17" s="124"/>
+      <c r="N17" s="142"/>
       <c r="O17" s="45"/>
       <c r="P17" s="12"/>
       <c r="Q17" s="12"/>
@@ -4903,10 +4903,10 @@
       </c>
     </row>
     <row r="18" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="123" t="s">
+      <c r="A18" s="140" t="s">
         <v>21</v>
       </c>
-      <c r="B18" s="124"/>
+      <c r="B18" s="142"/>
       <c r="C18" s="45"/>
       <c r="D18" s="12"/>
       <c r="E18" s="12"/>
@@ -4926,10 +4926,10 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M18" s="123" t="s">
+      <c r="M18" s="140" t="s">
         <v>21</v>
       </c>
-      <c r="N18" s="124"/>
+      <c r="N18" s="142"/>
       <c r="O18" s="45"/>
       <c r="P18" s="12"/>
       <c r="Q18" s="12"/>
@@ -4943,10 +4943,10 @@
       </c>
     </row>
     <row r="19" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="123" t="s">
+      <c r="A19" s="140" t="s">
         <v>22</v>
       </c>
-      <c r="B19" s="124"/>
+      <c r="B19" s="142"/>
       <c r="C19" s="47"/>
       <c r="D19" s="48"/>
       <c r="E19" s="48"/>
@@ -4963,10 +4963,10 @@
         <v>0</v>
       </c>
       <c r="L19" s="12"/>
-      <c r="M19" s="123" t="s">
+      <c r="M19" s="140" t="s">
         <v>22</v>
       </c>
-      <c r="N19" s="124"/>
+      <c r="N19" s="142"/>
       <c r="O19" s="47"/>
       <c r="P19" s="48"/>
       <c r="Q19" s="48"/>
@@ -4977,38 +4977,38 @@
       <c r="V19" s="12"/>
     </row>
     <row r="20" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="123" t="s">
+      <c r="A20" s="140" t="s">
         <v>23</v>
       </c>
-      <c r="B20" s="127"/>
-      <c r="C20" s="141"/>
-      <c r="D20" s="141"/>
-      <c r="E20" s="141"/>
-      <c r="F20" s="141"/>
-      <c r="G20" s="141"/>
-      <c r="H20" s="141"/>
-      <c r="I20" s="142"/>
+      <c r="B20" s="141"/>
+      <c r="C20" s="153"/>
+      <c r="D20" s="153"/>
+      <c r="E20" s="153"/>
+      <c r="F20" s="153"/>
+      <c r="G20" s="153"/>
+      <c r="H20" s="153"/>
+      <c r="I20" s="154"/>
       <c r="J20" s="34"/>
       <c r="K20" s="34"/>
       <c r="L20" s="12"/>
-      <c r="M20" s="123" t="s">
+      <c r="M20" s="140" t="s">
         <v>23</v>
       </c>
-      <c r="N20" s="127"/>
-      <c r="O20" s="141"/>
-      <c r="P20" s="141"/>
-      <c r="Q20" s="141"/>
-      <c r="R20" s="141"/>
-      <c r="S20" s="141"/>
-      <c r="T20" s="141"/>
-      <c r="U20" s="142"/>
+      <c r="N20" s="141"/>
+      <c r="O20" s="153"/>
+      <c r="P20" s="153"/>
+      <c r="Q20" s="153"/>
+      <c r="R20" s="153"/>
+      <c r="S20" s="153"/>
+      <c r="T20" s="153"/>
+      <c r="U20" s="154"/>
       <c r="V20" s="12"/>
     </row>
     <row r="21" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="123" t="s">
+      <c r="A21" s="140" t="s">
         <v>7</v>
       </c>
-      <c r="B21" s="124"/>
+      <c r="B21" s="142"/>
       <c r="C21" s="42"/>
       <c r="D21" s="43"/>
       <c r="E21" s="43"/>
@@ -5028,10 +5028,10 @@
         <f t="shared" ref="L21:L23" si="2">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C21:I21)&amp;","</f>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M21" s="123" t="s">
+      <c r="M21" s="140" t="s">
         <v>7</v>
       </c>
-      <c r="N21" s="124"/>
+      <c r="N21" s="142"/>
       <c r="O21" s="42"/>
       <c r="P21" s="43"/>
       <c r="Q21" s="43"/>
@@ -5045,10 +5045,10 @@
       </c>
     </row>
     <row r="22" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="125" t="s">
+      <c r="A22" s="145" t="s">
         <v>8</v>
       </c>
-      <c r="B22" s="126"/>
+      <c r="B22" s="146"/>
       <c r="C22" s="45"/>
       <c r="D22" s="12"/>
       <c r="E22" s="12"/>
@@ -5068,10 +5068,10 @@
         <f t="shared" si="2"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M22" s="123" t="s">
+      <c r="M22" s="140" t="s">
         <v>8</v>
       </c>
-      <c r="N22" s="124"/>
+      <c r="N22" s="142"/>
       <c r="O22" s="45"/>
       <c r="P22" s="12"/>
       <c r="Q22" s="12"/>
@@ -5085,10 +5085,10 @@
       </c>
     </row>
     <row r="23" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="123" t="s">
+      <c r="A23" s="140" t="s">
         <v>21</v>
       </c>
-      <c r="B23" s="124"/>
+      <c r="B23" s="142"/>
       <c r="C23" s="45"/>
       <c r="D23" s="12"/>
       <c r="E23" s="12"/>
@@ -5108,10 +5108,10 @@
         <f t="shared" si="2"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M23" s="123" t="s">
+      <c r="M23" s="140" t="s">
         <v>21</v>
       </c>
-      <c r="N23" s="124"/>
+      <c r="N23" s="142"/>
       <c r="O23" s="45"/>
       <c r="P23" s="12"/>
       <c r="Q23" s="12"/>
@@ -5125,10 +5125,10 @@
       </c>
     </row>
     <row r="24" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="123" t="s">
+      <c r="A24" s="140" t="s">
         <v>22</v>
       </c>
-      <c r="B24" s="124"/>
+      <c r="B24" s="142"/>
       <c r="C24" s="47"/>
       <c r="D24" s="48"/>
       <c r="E24" s="48"/>
@@ -5145,10 +5145,10 @@
         <v>0</v>
       </c>
       <c r="L24" s="12"/>
-      <c r="M24" s="123" t="s">
+      <c r="M24" s="140" t="s">
         <v>22</v>
       </c>
-      <c r="N24" s="124"/>
+      <c r="N24" s="142"/>
       <c r="O24" s="47"/>
       <c r="P24" s="48"/>
       <c r="Q24" s="48"/>
@@ -5159,38 +5159,38 @@
       <c r="V24" s="12"/>
     </row>
     <row r="25" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="123" t="s">
+      <c r="A25" s="140" t="s">
         <v>24</v>
       </c>
-      <c r="B25" s="127"/>
-      <c r="C25" s="141"/>
-      <c r="D25" s="141"/>
-      <c r="E25" s="141"/>
-      <c r="F25" s="141"/>
-      <c r="G25" s="141"/>
-      <c r="H25" s="141"/>
-      <c r="I25" s="142"/>
+      <c r="B25" s="141"/>
+      <c r="C25" s="153"/>
+      <c r="D25" s="153"/>
+      <c r="E25" s="153"/>
+      <c r="F25" s="153"/>
+      <c r="G25" s="153"/>
+      <c r="H25" s="153"/>
+      <c r="I25" s="154"/>
       <c r="J25" s="34"/>
       <c r="K25" s="34"/>
       <c r="L25" s="12"/>
-      <c r="M25" s="123" t="s">
+      <c r="M25" s="140" t="s">
         <v>23</v>
       </c>
-      <c r="N25" s="127"/>
-      <c r="O25" s="141"/>
-      <c r="P25" s="141"/>
-      <c r="Q25" s="141"/>
-      <c r="R25" s="141"/>
-      <c r="S25" s="141"/>
-      <c r="T25" s="141"/>
-      <c r="U25" s="142"/>
+      <c r="N25" s="141"/>
+      <c r="O25" s="153"/>
+      <c r="P25" s="153"/>
+      <c r="Q25" s="153"/>
+      <c r="R25" s="153"/>
+      <c r="S25" s="153"/>
+      <c r="T25" s="153"/>
+      <c r="U25" s="154"/>
       <c r="V25" s="12"/>
     </row>
     <row r="26" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="123" t="s">
+      <c r="A26" s="140" t="s">
         <v>7</v>
       </c>
-      <c r="B26" s="124"/>
+      <c r="B26" s="142"/>
       <c r="C26"/>
       <c r="D26"/>
       <c r="E26"/>
@@ -5210,10 +5210,10 @@
         <f t="shared" ref="L26:L28" si="4">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C26:I26)&amp;","</f>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M26" s="123" t="s">
+      <c r="M26" s="140" t="s">
         <v>7</v>
       </c>
-      <c r="N26" s="124"/>
+      <c r="N26" s="142"/>
       <c r="O26"/>
       <c r="P26"/>
       <c r="Q26"/>
@@ -5227,10 +5227,10 @@
       </c>
     </row>
     <row r="27" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="125" t="s">
+      <c r="A27" s="145" t="s">
         <v>8</v>
       </c>
-      <c r="B27" s="126"/>
+      <c r="B27" s="146"/>
       <c r="C27"/>
       <c r="D27"/>
       <c r="E27"/>
@@ -5250,10 +5250,10 @@
         <f t="shared" si="4"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M27" s="123" t="s">
+      <c r="M27" s="140" t="s">
         <v>8</v>
       </c>
-      <c r="N27" s="124"/>
+      <c r="N27" s="142"/>
       <c r="O27"/>
       <c r="P27"/>
       <c r="Q27"/>
@@ -5267,10 +5267,10 @@
       </c>
     </row>
     <row r="28" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="123" t="s">
+      <c r="A28" s="140" t="s">
         <v>21</v>
       </c>
-      <c r="B28" s="124"/>
+      <c r="B28" s="142"/>
       <c r="C28"/>
       <c r="D28"/>
       <c r="E28"/>
@@ -5290,10 +5290,10 @@
         <f t="shared" si="4"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M28" s="123" t="s">
+      <c r="M28" s="140" t="s">
         <v>21</v>
       </c>
-      <c r="N28" s="124"/>
+      <c r="N28" s="142"/>
       <c r="O28"/>
       <c r="P28"/>
       <c r="Q28"/>
@@ -5307,10 +5307,10 @@
       </c>
     </row>
     <row r="29" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="123" t="s">
+      <c r="A29" s="140" t="s">
         <v>22</v>
       </c>
-      <c r="B29" s="124"/>
+      <c r="B29" s="142"/>
       <c r="C29"/>
       <c r="D29"/>
       <c r="E29"/>
@@ -5327,10 +5327,10 @@
         <v>0</v>
       </c>
       <c r="L29" s="12"/>
-      <c r="M29" s="123" t="s">
+      <c r="M29" s="140" t="s">
         <v>22</v>
       </c>
-      <c r="N29" s="124"/>
+      <c r="N29" s="142"/>
       <c r="O29" s="73"/>
       <c r="P29" s="74"/>
       <c r="Q29" s="74"/>
@@ -5423,10 +5423,10 @@
       <c r="V31" s="1"/>
     </row>
     <row r="32" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="131" t="s">
+      <c r="A32" s="134" t="s">
         <v>5</v>
       </c>
-      <c r="B32" s="140"/>
+      <c r="B32" s="136"/>
       <c r="C32" s="36"/>
       <c r="D32" s="36"/>
       <c r="E32" s="36"/>
@@ -5440,10 +5440,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C32:I32)&amp;","</f>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M32" s="131" t="s">
+      <c r="M32" s="134" t="s">
         <v>5</v>
       </c>
-      <c r="N32" s="140"/>
+      <c r="N32" s="136"/>
       <c r="O32" s="35"/>
       <c r="P32" s="36"/>
       <c r="Q32" s="36"/>
@@ -5457,10 +5457,10 @@
       </c>
     </row>
     <row r="33" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="131" t="s">
+      <c r="A33" s="134" t="s">
         <v>6</v>
       </c>
-      <c r="B33" s="140"/>
+      <c r="B33" s="136"/>
       <c r="C33" s="36"/>
       <c r="D33" s="36"/>
       <c r="E33" s="36"/>
@@ -5474,10 +5474,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C33:I33)&amp;","</f>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M33" s="131" t="s">
+      <c r="M33" s="134" t="s">
         <v>6</v>
       </c>
-      <c r="N33" s="140"/>
+      <c r="N33" s="136"/>
       <c r="O33" s="36"/>
       <c r="P33" s="36"/>
       <c r="Q33" s="36"/>
@@ -5491,10 +5491,10 @@
       </c>
     </row>
     <row r="34" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="131" t="s">
+      <c r="A34" s="134" t="s">
         <v>10</v>
       </c>
-      <c r="B34" s="140"/>
+      <c r="B34" s="136"/>
       <c r="C34" s="28"/>
       <c r="D34" s="29"/>
       <c r="E34" s="29"/>
@@ -5508,10 +5508,10 @@
         <f t="shared" ref="L34:L43" si="7">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C34:I34)&amp;","</f>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M34" s="131" t="s">
+      <c r="M34" s="134" t="s">
         <v>10</v>
       </c>
-      <c r="N34" s="140"/>
+      <c r="N34" s="136"/>
       <c r="O34" s="28"/>
       <c r="P34" s="29"/>
       <c r="Q34" s="29"/>
@@ -5525,35 +5525,35 @@
       </c>
     </row>
     <row r="35" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="131" t="s">
+      <c r="A35" s="134" t="s">
         <v>12</v>
       </c>
-      <c r="B35" s="132"/>
-      <c r="C35" s="132"/>
-      <c r="D35" s="132"/>
-      <c r="E35" s="132"/>
-      <c r="F35" s="132"/>
-      <c r="G35" s="132"/>
-      <c r="H35" s="132"/>
-      <c r="I35" s="140"/>
+      <c r="B35" s="135"/>
+      <c r="C35" s="135"/>
+      <c r="D35" s="135"/>
+      <c r="E35" s="135"/>
+      <c r="F35" s="135"/>
+      <c r="G35" s="135"/>
+      <c r="H35" s="135"/>
+      <c r="I35" s="136"/>
       <c r="J35" s="38"/>
       <c r="K35" s="38"/>
       <c r="L35" s="1"/>
-      <c r="M35" s="131" t="s">
+      <c r="M35" s="134" t="s">
         <v>12</v>
       </c>
-      <c r="N35" s="132"/>
-      <c r="O35" s="132"/>
-      <c r="P35" s="132"/>
-      <c r="Q35" s="132"/>
-      <c r="R35" s="132"/>
-      <c r="S35" s="132"/>
-      <c r="T35" s="132"/>
-      <c r="U35" s="140"/>
+      <c r="N35" s="135"/>
+      <c r="O35" s="135"/>
+      <c r="P35" s="135"/>
+      <c r="Q35" s="135"/>
+      <c r="R35" s="135"/>
+      <c r="S35" s="135"/>
+      <c r="T35" s="135"/>
+      <c r="U35" s="136"/>
       <c r="V35" s="1"/>
     </row>
     <row r="36" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="133" t="s">
+      <c r="A36" s="132" t="s">
         <v>11</v>
       </c>
       <c r="B36" s="9" t="s">
@@ -5572,7 +5572,7 @@
         <f t="shared" si="7"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M36" s="133" t="s">
+      <c r="M36" s="132" t="s">
         <v>11</v>
       </c>
       <c r="N36" s="9" t="s">
@@ -5591,7 +5591,7 @@
       </c>
     </row>
     <row r="37" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="145"/>
+      <c r="A37" s="151"/>
       <c r="B37" s="9" t="s">
         <v>14</v>
       </c>
@@ -5608,7 +5608,7 @@
         <f t="shared" si="7"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M37" s="145"/>
+      <c r="M37" s="151"/>
       <c r="N37" s="9" t="s">
         <v>14</v>
       </c>
@@ -5625,7 +5625,7 @@
       </c>
     </row>
     <row r="38" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="145"/>
+      <c r="A38" s="151"/>
       <c r="B38" s="9" t="s">
         <v>17</v>
       </c>
@@ -5639,7 +5639,7 @@
       <c r="J38" s="38"/>
       <c r="K38" s="38"/>
       <c r="L38" s="1"/>
-      <c r="M38" s="145"/>
+      <c r="M38" s="151"/>
       <c r="N38" s="9" t="s">
         <v>17</v>
       </c>
@@ -5653,7 +5653,7 @@
       <c r="V38" s="1"/>
     </row>
     <row r="39" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="145"/>
+      <c r="A39" s="151"/>
       <c r="B39" s="9" t="s">
         <v>18</v>
       </c>
@@ -5667,7 +5667,7 @@
       <c r="J39" s="38"/>
       <c r="K39" s="38"/>
       <c r="L39" s="1"/>
-      <c r="M39" s="145"/>
+      <c r="M39" s="151"/>
       <c r="N39" s="9" t="s">
         <v>18</v>
       </c>
@@ -5681,7 +5681,7 @@
       <c r="V39" s="1"/>
     </row>
     <row r="40" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="145"/>
+      <c r="A40" s="151"/>
       <c r="B40" s="9" t="s">
         <v>15</v>
       </c>
@@ -5698,7 +5698,7 @@
         <f t="shared" si="7"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M40" s="145"/>
+      <c r="M40" s="151"/>
       <c r="N40" s="9" t="s">
         <v>15</v>
       </c>
@@ -5712,7 +5712,7 @@
       <c r="V40" s="1"/>
     </row>
     <row r="41" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="145"/>
+      <c r="A41" s="151"/>
       <c r="B41" s="9" t="s">
         <v>25</v>
       </c>
@@ -5726,7 +5726,7 @@
       <c r="J41" s="38"/>
       <c r="K41" s="38"/>
       <c r="L41" s="1"/>
-      <c r="M41" s="145"/>
+      <c r="M41" s="151"/>
       <c r="N41" s="9" t="s">
         <v>25</v>
       </c>
@@ -5740,7 +5740,7 @@
       <c r="V41" s="1"/>
     </row>
     <row r="42" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="145"/>
+      <c r="A42" s="151"/>
       <c r="B42" s="9" t="s">
         <v>19</v>
       </c>
@@ -5754,7 +5754,7 @@
       <c r="J42" s="38"/>
       <c r="K42" s="38"/>
       <c r="L42" s="1"/>
-      <c r="M42" s="145"/>
+      <c r="M42" s="151"/>
       <c r="N42" s="9" t="s">
         <v>19</v>
       </c>
@@ -5768,7 +5768,7 @@
       <c r="V42" s="1"/>
     </row>
     <row r="43" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="145"/>
+      <c r="A43" s="151"/>
       <c r="B43" s="9" t="s">
         <v>16</v>
       </c>
@@ -5785,7 +5785,7 @@
         <f t="shared" si="7"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M43" s="145"/>
+      <c r="M43" s="151"/>
       <c r="N43" s="9" t="s">
         <v>16</v>
       </c>
@@ -5799,7 +5799,7 @@
       <c r="V43" s="1"/>
     </row>
     <row r="44" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="139"/>
+      <c r="A44" s="130"/>
       <c r="B44" s="9" t="s">
         <v>26</v>
       </c>
@@ -5813,7 +5813,7 @@
       <c r="J44" s="38"/>
       <c r="K44" s="38"/>
       <c r="L44" s="1"/>
-      <c r="M44" s="139"/>
+      <c r="M44" s="130"/>
       <c r="N44" s="9" t="s">
         <v>26</v>
       </c>
@@ -5827,38 +5827,38 @@
       <c r="V44" s="1"/>
     </row>
     <row r="45" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="131" t="s">
+      <c r="A45" s="134" t="s">
         <v>20</v>
       </c>
-      <c r="B45" s="132"/>
-      <c r="C45" s="136"/>
-      <c r="D45" s="136"/>
-      <c r="E45" s="136"/>
-      <c r="F45" s="136"/>
-      <c r="G45" s="136"/>
-      <c r="H45" s="136"/>
-      <c r="I45" s="143"/>
+      <c r="B45" s="135"/>
+      <c r="C45" s="137"/>
+      <c r="D45" s="137"/>
+      <c r="E45" s="137"/>
+      <c r="F45" s="137"/>
+      <c r="G45" s="137"/>
+      <c r="H45" s="137"/>
+      <c r="I45" s="152"/>
       <c r="J45" s="38"/>
       <c r="K45" s="38"/>
       <c r="L45" s="1"/>
-      <c r="M45" s="131" t="s">
+      <c r="M45" s="134" t="s">
         <v>20</v>
       </c>
-      <c r="N45" s="132"/>
-      <c r="O45" s="136"/>
-      <c r="P45" s="136"/>
-      <c r="Q45" s="136"/>
-      <c r="R45" s="136"/>
-      <c r="S45" s="136"/>
-      <c r="T45" s="136"/>
-      <c r="U45" s="143"/>
+      <c r="N45" s="135"/>
+      <c r="O45" s="137"/>
+      <c r="P45" s="137"/>
+      <c r="Q45" s="137"/>
+      <c r="R45" s="137"/>
+      <c r="S45" s="137"/>
+      <c r="T45" s="137"/>
+      <c r="U45" s="152"/>
       <c r="V45" s="1"/>
     </row>
     <row r="46" spans="1:22" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="131" t="s">
+      <c r="A46" s="134" t="s">
         <v>7</v>
       </c>
-      <c r="B46" s="140"/>
+      <c r="B46" s="136"/>
       <c r="C46" s="50"/>
       <c r="D46" s="51"/>
       <c r="E46" s="51"/>
@@ -5872,10 +5872,10 @@
         <f t="shared" ref="L46:L48" si="8">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C46:I46)&amp;","</f>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M46" s="131" t="s">
+      <c r="M46" s="134" t="s">
         <v>7</v>
       </c>
-      <c r="N46" s="140"/>
+      <c r="N46" s="136"/>
       <c r="O46" s="50"/>
       <c r="P46" s="51"/>
       <c r="Q46" s="51"/>
@@ -5889,10 +5889,10 @@
       </c>
     </row>
     <row r="47" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="131" t="s">
+      <c r="A47" s="134" t="s">
         <v>8</v>
       </c>
-      <c r="B47" s="140"/>
+      <c r="B47" s="136"/>
       <c r="C47" s="53"/>
       <c r="D47" s="1"/>
       <c r="E47" s="1"/>
@@ -5906,10 +5906,10 @@
         <f t="shared" si="8"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M47" s="131" t="s">
+      <c r="M47" s="134" t="s">
         <v>8</v>
       </c>
-      <c r="N47" s="140"/>
+      <c r="N47" s="136"/>
       <c r="O47" s="53"/>
       <c r="P47" s="1"/>
       <c r="Q47" s="1"/>
@@ -5923,10 +5923,10 @@
       </c>
     </row>
     <row r="48" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="131" t="s">
+      <c r="A48" s="134" t="s">
         <v>21</v>
       </c>
-      <c r="B48" s="140"/>
+      <c r="B48" s="136"/>
       <c r="C48" s="53"/>
       <c r="D48" s="1"/>
       <c r="E48" s="1"/>
@@ -5940,10 +5940,10 @@
         <f t="shared" si="8"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M48" s="131" t="s">
+      <c r="M48" s="134" t="s">
         <v>21</v>
       </c>
-      <c r="N48" s="140"/>
+      <c r="N48" s="136"/>
       <c r="O48" s="53"/>
       <c r="P48" s="1"/>
       <c r="Q48" s="1"/>
@@ -5957,10 +5957,10 @@
       </c>
     </row>
     <row r="49" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="131" t="s">
+      <c r="A49" s="134" t="s">
         <v>22</v>
       </c>
-      <c r="B49" s="140"/>
+      <c r="B49" s="136"/>
       <c r="C49" s="55"/>
       <c r="D49" s="56"/>
       <c r="E49" s="56"/>
@@ -5971,10 +5971,10 @@
       <c r="J49" s="41"/>
       <c r="K49" s="41"/>
       <c r="L49" s="40"/>
-      <c r="M49" s="131" t="s">
+      <c r="M49" s="134" t="s">
         <v>22</v>
       </c>
-      <c r="N49" s="140"/>
+      <c r="N49" s="136"/>
       <c r="O49" s="55"/>
       <c r="P49" s="56"/>
       <c r="Q49" s="56"/>
@@ -5985,38 +5985,38 @@
       <c r="V49" s="1"/>
     </row>
     <row r="50" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="131" t="s">
+      <c r="A50" s="134" t="s">
         <v>23</v>
       </c>
-      <c r="B50" s="132"/>
-      <c r="C50" s="136"/>
-      <c r="D50" s="136"/>
-      <c r="E50" s="136"/>
-      <c r="F50" s="136"/>
-      <c r="G50" s="136"/>
-      <c r="H50" s="136"/>
-      <c r="I50" s="143"/>
+      <c r="B50" s="135"/>
+      <c r="C50" s="137"/>
+      <c r="D50" s="137"/>
+      <c r="E50" s="137"/>
+      <c r="F50" s="137"/>
+      <c r="G50" s="137"/>
+      <c r="H50" s="137"/>
+      <c r="I50" s="152"/>
       <c r="J50" s="38"/>
       <c r="K50" s="38"/>
       <c r="L50" s="1"/>
-      <c r="M50" s="131" t="s">
+      <c r="M50" s="134" t="s">
         <v>23</v>
       </c>
-      <c r="N50" s="132"/>
-      <c r="O50" s="136"/>
-      <c r="P50" s="136"/>
-      <c r="Q50" s="136"/>
-      <c r="R50" s="136"/>
-      <c r="S50" s="136"/>
-      <c r="T50" s="136"/>
-      <c r="U50" s="143"/>
+      <c r="N50" s="135"/>
+      <c r="O50" s="137"/>
+      <c r="P50" s="137"/>
+      <c r="Q50" s="137"/>
+      <c r="R50" s="137"/>
+      <c r="S50" s="137"/>
+      <c r="T50" s="137"/>
+      <c r="U50" s="152"/>
       <c r="V50" s="1"/>
     </row>
     <row r="51" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="131" t="s">
+      <c r="A51" s="134" t="s">
         <v>7</v>
       </c>
-      <c r="B51" s="140"/>
+      <c r="B51" s="136"/>
       <c r="C51" s="50"/>
       <c r="D51" s="51"/>
       <c r="E51" s="51"/>
@@ -6030,10 +6030,10 @@
         <f t="shared" ref="L51:L53" si="9">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C51:I51)&amp;","</f>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M51" s="131" t="s">
+      <c r="M51" s="134" t="s">
         <v>7</v>
       </c>
-      <c r="N51" s="140"/>
+      <c r="N51" s="136"/>
       <c r="O51" s="50"/>
       <c r="P51" s="51"/>
       <c r="Q51" s="51"/>
@@ -6047,10 +6047,10 @@
       </c>
     </row>
     <row r="52" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="133" t="s">
+      <c r="A52" s="132" t="s">
         <v>8</v>
       </c>
-      <c r="B52" s="135"/>
+      <c r="B52" s="139"/>
       <c r="C52" s="53"/>
       <c r="D52" s="1"/>
       <c r="E52" s="1"/>
@@ -6064,10 +6064,10 @@
         <f t="shared" si="9"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M52" s="131" t="s">
+      <c r="M52" s="134" t="s">
         <v>8</v>
       </c>
-      <c r="N52" s="140"/>
+      <c r="N52" s="136"/>
       <c r="O52" s="53"/>
       <c r="P52" s="1"/>
       <c r="Q52" s="1"/>
@@ -6081,10 +6081,10 @@
       </c>
     </row>
     <row r="53" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="131" t="s">
+      <c r="A53" s="134" t="s">
         <v>21</v>
       </c>
-      <c r="B53" s="140"/>
+      <c r="B53" s="136"/>
       <c r="C53" s="53"/>
       <c r="D53" s="1"/>
       <c r="E53" s="1"/>
@@ -6098,10 +6098,10 @@
         <f t="shared" si="9"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M53" s="131" t="s">
+      <c r="M53" s="134" t="s">
         <v>21</v>
       </c>
-      <c r="N53" s="140"/>
+      <c r="N53" s="136"/>
       <c r="O53" s="53"/>
       <c r="P53" s="1"/>
       <c r="Q53" s="1"/>
@@ -6115,10 +6115,10 @@
       </c>
     </row>
     <row r="54" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="131" t="s">
+      <c r="A54" s="134" t="s">
         <v>22</v>
       </c>
-      <c r="B54" s="140"/>
+      <c r="B54" s="136"/>
       <c r="C54" s="55"/>
       <c r="D54" s="56"/>
       <c r="E54" s="56"/>
@@ -6129,10 +6129,10 @@
       <c r="J54" s="38"/>
       <c r="K54" s="38"/>
       <c r="L54" s="1"/>
-      <c r="M54" s="131" t="s">
+      <c r="M54" s="134" t="s">
         <v>22</v>
       </c>
-      <c r="N54" s="140"/>
+      <c r="N54" s="136"/>
       <c r="O54" s="55"/>
       <c r="P54" s="56"/>
       <c r="Q54" s="56"/>
@@ -6143,38 +6143,38 @@
       <c r="V54" s="1"/>
     </row>
     <row r="55" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="131" t="s">
+      <c r="A55" s="134" t="s">
         <v>24</v>
       </c>
-      <c r="B55" s="132"/>
-      <c r="C55" s="136"/>
-      <c r="D55" s="136"/>
-      <c r="E55" s="136"/>
-      <c r="F55" s="136"/>
-      <c r="G55" s="136"/>
-      <c r="H55" s="136"/>
-      <c r="I55" s="143"/>
+      <c r="B55" s="135"/>
+      <c r="C55" s="137"/>
+      <c r="D55" s="137"/>
+      <c r="E55" s="137"/>
+      <c r="F55" s="137"/>
+      <c r="G55" s="137"/>
+      <c r="H55" s="137"/>
+      <c r="I55" s="152"/>
       <c r="J55" s="38"/>
       <c r="K55" s="38"/>
       <c r="L55" s="1"/>
-      <c r="M55" s="131" t="s">
+      <c r="M55" s="134" t="s">
         <v>23</v>
       </c>
-      <c r="N55" s="132"/>
-      <c r="O55" s="136"/>
-      <c r="P55" s="136"/>
-      <c r="Q55" s="136"/>
-      <c r="R55" s="136"/>
-      <c r="S55" s="136"/>
-      <c r="T55" s="136"/>
-      <c r="U55" s="143"/>
+      <c r="N55" s="135"/>
+      <c r="O55" s="137"/>
+      <c r="P55" s="137"/>
+      <c r="Q55" s="137"/>
+      <c r="R55" s="137"/>
+      <c r="S55" s="137"/>
+      <c r="T55" s="137"/>
+      <c r="U55" s="152"/>
       <c r="V55" s="1"/>
     </row>
     <row r="56" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="131" t="s">
+      <c r="A56" s="134" t="s">
         <v>7</v>
       </c>
-      <c r="B56" s="140"/>
+      <c r="B56" s="136"/>
       <c r="C56"/>
       <c r="D56"/>
       <c r="E56"/>
@@ -6188,10 +6188,10 @@
         <f t="shared" ref="L56:L58" si="11">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C56:I56)&amp;","</f>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M56" s="131" t="s">
+      <c r="M56" s="134" t="s">
         <v>7</v>
       </c>
-      <c r="N56" s="140"/>
+      <c r="N56" s="136"/>
       <c r="O56"/>
       <c r="P56"/>
       <c r="Q56"/>
@@ -6205,10 +6205,10 @@
       </c>
     </row>
     <row r="57" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="133" t="s">
+      <c r="A57" s="132" t="s">
         <v>8</v>
       </c>
-      <c r="B57" s="135"/>
+      <c r="B57" s="139"/>
       <c r="C57"/>
       <c r="D57"/>
       <c r="E57"/>
@@ -6222,10 +6222,10 @@
         <f t="shared" si="11"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M57" s="131" t="s">
+      <c r="M57" s="134" t="s">
         <v>8</v>
       </c>
-      <c r="N57" s="140"/>
+      <c r="N57" s="136"/>
       <c r="O57"/>
       <c r="P57"/>
       <c r="Q57"/>
@@ -6239,10 +6239,10 @@
       </c>
     </row>
     <row r="58" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="131" t="s">
+      <c r="A58" s="134" t="s">
         <v>21</v>
       </c>
-      <c r="B58" s="140"/>
+      <c r="B58" s="136"/>
       <c r="C58"/>
       <c r="D58"/>
       <c r="E58"/>
@@ -6256,10 +6256,10 @@
         <f t="shared" si="11"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M58" s="131" t="s">
+      <c r="M58" s="134" t="s">
         <v>21</v>
       </c>
-      <c r="N58" s="140"/>
+      <c r="N58" s="136"/>
       <c r="O58"/>
       <c r="P58"/>
       <c r="Q58"/>
@@ -6273,10 +6273,10 @@
       </c>
     </row>
     <row r="59" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="131" t="s">
+      <c r="A59" s="134" t="s">
         <v>22</v>
       </c>
-      <c r="B59" s="140"/>
+      <c r="B59" s="136"/>
       <c r="C59" s="70"/>
       <c r="D59" s="71"/>
       <c r="E59" s="71"/>
@@ -6287,10 +6287,10 @@
       <c r="J59" s="38"/>
       <c r="K59" s="38"/>
       <c r="L59" s="1"/>
-      <c r="M59" s="131" t="s">
+      <c r="M59" s="134" t="s">
         <v>22</v>
       </c>
-      <c r="N59" s="140"/>
+      <c r="N59" s="136"/>
       <c r="O59" s="70"/>
       <c r="P59" s="71"/>
       <c r="Q59" s="71"/>
@@ -6316,14 +6316,62 @@
     </row>
   </sheetData>
   <mergeCells count="80">
-    <mergeCell ref="A59:B59"/>
-    <mergeCell ref="M59:N59"/>
-    <mergeCell ref="A56:B56"/>
-    <mergeCell ref="M56:N56"/>
-    <mergeCell ref="A57:B57"/>
-    <mergeCell ref="M57:N57"/>
-    <mergeCell ref="A58:B58"/>
-    <mergeCell ref="M58:N58"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="M2:N2"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="M32:N32"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="M3:N3"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="A5:I5"/>
+    <mergeCell ref="M5:U5"/>
+    <mergeCell ref="M20:U20"/>
+    <mergeCell ref="A15:I15"/>
+    <mergeCell ref="A25:I25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="A48:B48"/>
+    <mergeCell ref="A49:B49"/>
+    <mergeCell ref="M48:N48"/>
+    <mergeCell ref="M49:N49"/>
+    <mergeCell ref="M16:N16"/>
+    <mergeCell ref="M17:N17"/>
+    <mergeCell ref="A46:B46"/>
+    <mergeCell ref="A47:B47"/>
+    <mergeCell ref="M46:N46"/>
+    <mergeCell ref="M47:N47"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="M33:N33"/>
+    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="M34:N34"/>
+    <mergeCell ref="A35:I35"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="A45:I45"/>
+    <mergeCell ref="M15:U15"/>
+    <mergeCell ref="M45:U45"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="M18:N18"/>
+    <mergeCell ref="M19:N19"/>
+    <mergeCell ref="M35:U35"/>
+    <mergeCell ref="A20:I20"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="M21:N21"/>
+    <mergeCell ref="M22:N22"/>
+    <mergeCell ref="M23:N23"/>
+    <mergeCell ref="M24:N24"/>
+    <mergeCell ref="A54:B54"/>
+    <mergeCell ref="M54:N54"/>
+    <mergeCell ref="A50:I50"/>
+    <mergeCell ref="M50:U50"/>
+    <mergeCell ref="A51:B51"/>
+    <mergeCell ref="M51:N51"/>
+    <mergeCell ref="A52:B52"/>
+    <mergeCell ref="M52:N52"/>
     <mergeCell ref="A6:A14"/>
     <mergeCell ref="M6:M14"/>
     <mergeCell ref="A36:A44"/>
@@ -6340,62 +6388,14 @@
     <mergeCell ref="M29:N29"/>
     <mergeCell ref="A53:B53"/>
     <mergeCell ref="M53:N53"/>
-    <mergeCell ref="A54:B54"/>
-    <mergeCell ref="M54:N54"/>
-    <mergeCell ref="A50:I50"/>
-    <mergeCell ref="M50:U50"/>
-    <mergeCell ref="A51:B51"/>
-    <mergeCell ref="M51:N51"/>
-    <mergeCell ref="A52:B52"/>
-    <mergeCell ref="M52:N52"/>
-    <mergeCell ref="A45:I45"/>
-    <mergeCell ref="M15:U15"/>
-    <mergeCell ref="M45:U45"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="M18:N18"/>
-    <mergeCell ref="M19:N19"/>
-    <mergeCell ref="M35:U35"/>
-    <mergeCell ref="A20:I20"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="M21:N21"/>
-    <mergeCell ref="M22:N22"/>
-    <mergeCell ref="M23:N23"/>
-    <mergeCell ref="M24:N24"/>
-    <mergeCell ref="A48:B48"/>
-    <mergeCell ref="A49:B49"/>
-    <mergeCell ref="M48:N48"/>
-    <mergeCell ref="M49:N49"/>
-    <mergeCell ref="M16:N16"/>
-    <mergeCell ref="M17:N17"/>
-    <mergeCell ref="A46:B46"/>
-    <mergeCell ref="A47:B47"/>
-    <mergeCell ref="M46:N46"/>
-    <mergeCell ref="M47:N47"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="M33:N33"/>
-    <mergeCell ref="A34:B34"/>
-    <mergeCell ref="M34:N34"/>
-    <mergeCell ref="A35:I35"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="M2:N2"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="M32:N32"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="M3:N3"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="A5:I5"/>
-    <mergeCell ref="M5:U5"/>
-    <mergeCell ref="M20:U20"/>
-    <mergeCell ref="A15:I15"/>
-    <mergeCell ref="A25:I25"/>
-    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="A59:B59"/>
+    <mergeCell ref="M59:N59"/>
+    <mergeCell ref="A56:B56"/>
+    <mergeCell ref="M56:N56"/>
+    <mergeCell ref="A57:B57"/>
+    <mergeCell ref="M57:N57"/>
+    <mergeCell ref="A58:B58"/>
+    <mergeCell ref="M58:N58"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C2:I4 C6:I14 C16:I19 C21:I24 C26:I29">
@@ -6467,17 +6467,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C9:I9">
+    <cfRule type="colorScale" priority="24">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="23">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="24">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -6511,17 +6511,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C12:I12">
+    <cfRule type="colorScale" priority="26">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="25">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="26">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -6859,20 +6859,20 @@
   <sheetData>
     <row r="2" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="3" spans="2:14" ht="15" x14ac:dyDescent="0.25">
-      <c r="B3" s="146" t="s">
+      <c r="B3" s="121" t="s">
         <v>33</v>
       </c>
-      <c r="C3" s="150"/>
-      <c r="D3" s="152" t="s">
+      <c r="C3" s="127"/>
+      <c r="D3" s="124" t="s">
         <v>31</v>
       </c>
-      <c r="E3" s="153"/>
-      <c r="F3" s="153"/>
-      <c r="G3" s="154"/>
+      <c r="E3" s="125"/>
+      <c r="F3" s="125"/>
+      <c r="G3" s="126"/>
     </row>
     <row r="4" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="148"/>
-      <c r="C4" s="151"/>
+      <c r="B4" s="123"/>
+      <c r="C4" s="128"/>
       <c r="D4" s="90" t="s">
         <v>27</v>
       </c>
@@ -6889,7 +6889,7 @@
       <c r="L4" s="25"/>
     </row>
     <row r="5" spans="2:14" ht="15" x14ac:dyDescent="0.25">
-      <c r="B5" s="146" t="s">
+      <c r="B5" s="121" t="s">
         <v>30</v>
       </c>
       <c r="C5" s="88" t="s">
@@ -6909,7 +6909,7 @@
       </c>
     </row>
     <row r="6" spans="2:14" ht="15" x14ac:dyDescent="0.25">
-      <c r="B6" s="147"/>
+      <c r="B6" s="122"/>
       <c r="C6" s="89" t="s">
         <v>28</v>
       </c>
@@ -6927,7 +6927,7 @@
       </c>
     </row>
     <row r="7" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="148"/>
+      <c r="B7" s="123"/>
       <c r="C7" s="67" t="s">
         <v>29</v>
       </c>
@@ -6969,30 +6969,30 @@
       <c r="G10" s="25"/>
     </row>
     <row r="11" spans="2:14" ht="15" x14ac:dyDescent="0.25">
-      <c r="B11" s="149" t="s">
+      <c r="B11" s="129" t="s">
         <v>37</v>
       </c>
-      <c r="C11" s="150"/>
-      <c r="D11" s="152" t="s">
+      <c r="C11" s="127"/>
+      <c r="D11" s="124" t="s">
         <v>31</v>
       </c>
-      <c r="E11" s="153"/>
-      <c r="F11" s="153"/>
-      <c r="G11" s="154"/>
-      <c r="I11" s="149" t="s">
+      <c r="E11" s="125"/>
+      <c r="F11" s="125"/>
+      <c r="G11" s="126"/>
+      <c r="I11" s="129" t="s">
         <v>38</v>
       </c>
-      <c r="J11" s="150"/>
-      <c r="K11" s="152" t="s">
+      <c r="J11" s="127"/>
+      <c r="K11" s="124" t="s">
         <v>31</v>
       </c>
-      <c r="L11" s="153"/>
-      <c r="M11" s="153"/>
-      <c r="N11" s="154"/>
+      <c r="L11" s="125"/>
+      <c r="M11" s="125"/>
+      <c r="N11" s="126"/>
     </row>
     <row r="12" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="148"/>
-      <c r="C12" s="151"/>
+      <c r="B12" s="123"/>
+      <c r="C12" s="128"/>
       <c r="D12" s="90" t="s">
         <v>27</v>
       </c>
@@ -7005,8 +7005,8 @@
       <c r="G12" s="66" t="s">
         <v>32</v>
       </c>
-      <c r="I12" s="148"/>
-      <c r="J12" s="151"/>
+      <c r="I12" s="123"/>
+      <c r="J12" s="128"/>
       <c r="K12" s="90" t="s">
         <v>27</v>
       </c>
@@ -7021,7 +7021,7 @@
       </c>
     </row>
     <row r="13" spans="2:14" ht="15" x14ac:dyDescent="0.25">
-      <c r="B13" s="146" t="s">
+      <c r="B13" s="121" t="s">
         <v>30</v>
       </c>
       <c r="C13" s="88" t="s">
@@ -7039,7 +7039,7 @@
       <c r="G13" s="113">
         <v>92.97</v>
       </c>
-      <c r="I13" s="146" t="s">
+      <c r="I13" s="121" t="s">
         <v>30</v>
       </c>
       <c r="J13" s="88" t="s">
@@ -7059,7 +7059,7 @@
       </c>
     </row>
     <row r="14" spans="2:14" ht="15" x14ac:dyDescent="0.25">
-      <c r="B14" s="147"/>
+      <c r="B14" s="122"/>
       <c r="C14" s="89" t="s">
         <v>28</v>
       </c>
@@ -7075,7 +7075,7 @@
       <c r="G14" s="92">
         <v>93.55</v>
       </c>
-      <c r="I14" s="147"/>
+      <c r="I14" s="122"/>
       <c r="J14" s="89" t="s">
         <v>28</v>
       </c>
@@ -7093,7 +7093,7 @@
       </c>
     </row>
     <row r="15" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="148"/>
+      <c r="B15" s="123"/>
       <c r="C15" s="67" t="s">
         <v>29</v>
       </c>
@@ -7109,7 +7109,7 @@
       <c r="G15" s="93">
         <v>88.64</v>
       </c>
-      <c r="I15" s="148"/>
+      <c r="I15" s="123"/>
       <c r="J15" s="67" t="s">
         <v>29</v>
       </c>
@@ -7128,40 +7128,40 @@
     </row>
     <row r="16" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="17" spans="2:21" ht="15" x14ac:dyDescent="0.25">
-      <c r="B17" s="149" t="s">
+      <c r="B17" s="129" t="s">
         <v>36</v>
       </c>
-      <c r="C17" s="150"/>
-      <c r="D17" s="152" t="s">
+      <c r="C17" s="127"/>
+      <c r="D17" s="124" t="s">
         <v>31</v>
       </c>
-      <c r="E17" s="153"/>
-      <c r="F17" s="153"/>
-      <c r="G17" s="154"/>
-      <c r="I17" s="149" t="s">
+      <c r="E17" s="125"/>
+      <c r="F17" s="125"/>
+      <c r="G17" s="126"/>
+      <c r="I17" s="129" t="s">
         <v>35</v>
       </c>
-      <c r="J17" s="150"/>
-      <c r="K17" s="152" t="s">
+      <c r="J17" s="127"/>
+      <c r="K17" s="124" t="s">
         <v>31</v>
       </c>
-      <c r="L17" s="153"/>
-      <c r="M17" s="153"/>
-      <c r="N17" s="154"/>
-      <c r="P17" s="149" t="s">
+      <c r="L17" s="125"/>
+      <c r="M17" s="125"/>
+      <c r="N17" s="126"/>
+      <c r="P17" s="129" t="s">
         <v>34</v>
       </c>
-      <c r="Q17" s="150"/>
-      <c r="R17" s="152" t="s">
+      <c r="Q17" s="127"/>
+      <c r="R17" s="124" t="s">
         <v>31</v>
       </c>
-      <c r="S17" s="153"/>
-      <c r="T17" s="153"/>
-      <c r="U17" s="154"/>
+      <c r="S17" s="125"/>
+      <c r="T17" s="125"/>
+      <c r="U17" s="126"/>
     </row>
     <row r="18" spans="2:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="148"/>
-      <c r="C18" s="151"/>
+      <c r="B18" s="123"/>
+      <c r="C18" s="128"/>
       <c r="D18" s="90" t="s">
         <v>27</v>
       </c>
@@ -7174,8 +7174,8 @@
       <c r="G18" s="66" t="s">
         <v>32</v>
       </c>
-      <c r="I18" s="148"/>
-      <c r="J18" s="151"/>
+      <c r="I18" s="123"/>
+      <c r="J18" s="128"/>
       <c r="K18" s="90" t="s">
         <v>27</v>
       </c>
@@ -7188,8 +7188,8 @@
       <c r="N18" s="66" t="s">
         <v>32</v>
       </c>
-      <c r="P18" s="148"/>
-      <c r="Q18" s="151"/>
+      <c r="P18" s="123"/>
+      <c r="Q18" s="128"/>
       <c r="R18" s="90" t="s">
         <v>27</v>
       </c>
@@ -7204,7 +7204,7 @@
       </c>
     </row>
     <row r="19" spans="2:21" ht="15" x14ac:dyDescent="0.25">
-      <c r="B19" s="146" t="s">
+      <c r="B19" s="121" t="s">
         <v>30</v>
       </c>
       <c r="C19" s="88" t="s">
@@ -7222,7 +7222,7 @@
       <c r="G19" s="113">
         <v>90.61</v>
       </c>
-      <c r="I19" s="146" t="s">
+      <c r="I19" s="121" t="s">
         <v>30</v>
       </c>
       <c r="J19" s="88" t="s">
@@ -7240,7 +7240,7 @@
       <c r="N19" s="113">
         <v>76.89</v>
       </c>
-      <c r="P19" s="146" t="s">
+      <c r="P19" s="121" t="s">
         <v>30</v>
       </c>
       <c r="Q19" s="88" t="s">
@@ -7260,7 +7260,7 @@
       </c>
     </row>
     <row r="20" spans="2:21" ht="15" x14ac:dyDescent="0.25">
-      <c r="B20" s="147"/>
+      <c r="B20" s="122"/>
       <c r="C20" s="89" t="s">
         <v>28</v>
       </c>
@@ -7276,7 +7276,7 @@
       <c r="G20" s="92">
         <v>90.5</v>
       </c>
-      <c r="I20" s="147"/>
+      <c r="I20" s="122"/>
       <c r="J20" s="89" t="s">
         <v>28</v>
       </c>
@@ -7292,7 +7292,7 @@
       <c r="N20" s="92">
         <v>72.8</v>
       </c>
-      <c r="P20" s="147"/>
+      <c r="P20" s="122"/>
       <c r="Q20" s="89" t="s">
         <v>28</v>
       </c>
@@ -7310,7 +7310,7 @@
       </c>
     </row>
     <row r="21" spans="2:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="148"/>
+      <c r="B21" s="123"/>
       <c r="C21" s="67" t="s">
         <v>29</v>
       </c>
@@ -7326,7 +7326,7 @@
       <c r="G21" s="93">
         <v>87.1</v>
       </c>
-      <c r="I21" s="148"/>
+      <c r="I21" s="123"/>
       <c r="J21" s="67" t="s">
         <v>29</v>
       </c>
@@ -7342,7 +7342,7 @@
       <c r="N21" s="93">
         <v>74.819999999999993</v>
       </c>
-      <c r="P21" s="148"/>
+      <c r="P21" s="123"/>
       <c r="Q21" s="67" t="s">
         <v>29</v>
       </c>
@@ -7361,6 +7361,14 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="P19:P21"/>
+    <mergeCell ref="I17:J18"/>
+    <mergeCell ref="K17:N17"/>
+    <mergeCell ref="I19:I21"/>
+    <mergeCell ref="B17:C18"/>
+    <mergeCell ref="D17:G17"/>
+    <mergeCell ref="B19:B21"/>
+    <mergeCell ref="P17:Q18"/>
     <mergeCell ref="B5:B7"/>
     <mergeCell ref="D3:G3"/>
     <mergeCell ref="B3:C4"/>
@@ -7371,14 +7379,6 @@
     <mergeCell ref="K11:N11"/>
     <mergeCell ref="B13:B15"/>
     <mergeCell ref="I13:I15"/>
-    <mergeCell ref="P19:P21"/>
-    <mergeCell ref="I17:J18"/>
-    <mergeCell ref="K17:N17"/>
-    <mergeCell ref="I19:I21"/>
-    <mergeCell ref="B17:C18"/>
-    <mergeCell ref="D17:G17"/>
-    <mergeCell ref="B19:B21"/>
-    <mergeCell ref="P17:Q18"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="D5:F7">
@@ -7879,16 +7879,16 @@
     </row>
     <row r="3" spans="1:22" ht="15" x14ac:dyDescent="0.25">
       <c r="A3" s="94"/>
-      <c r="B3" s="158" t="s">
+      <c r="B3" s="163" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="162"/>
-      <c r="D3" s="155" t="s">
+      <c r="C3" s="157"/>
+      <c r="D3" s="160" t="s">
         <v>31</v>
       </c>
-      <c r="E3" s="156"/>
-      <c r="F3" s="156"/>
-      <c r="G3" s="157"/>
+      <c r="E3" s="161"/>
+      <c r="F3" s="161"/>
+      <c r="G3" s="162"/>
       <c r="H3" s="94"/>
       <c r="I3" s="94"/>
       <c r="J3" s="94"/>
@@ -7907,8 +7907,8 @@
     </row>
     <row r="4" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="94"/>
-      <c r="B4" s="160"/>
-      <c r="C4" s="163"/>
+      <c r="B4" s="158"/>
+      <c r="C4" s="159"/>
       <c r="D4" s="96" t="s">
         <v>32</v>
       </c>
@@ -7939,7 +7939,7 @@
     </row>
     <row r="5" spans="1:22" ht="15" x14ac:dyDescent="0.25">
       <c r="A5" s="94"/>
-      <c r="B5" s="158" t="s">
+      <c r="B5" s="163" t="s">
         <v>30</v>
       </c>
       <c r="C5" s="95" t="s">
@@ -7975,7 +7975,7 @@
     </row>
     <row r="6" spans="1:22" ht="15" x14ac:dyDescent="0.25">
       <c r="A6" s="94"/>
-      <c r="B6" s="159"/>
+      <c r="B6" s="164"/>
       <c r="C6" s="96" t="s">
         <v>28</v>
       </c>
@@ -8009,7 +8009,7 @@
     </row>
     <row r="7" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="94"/>
-      <c r="B7" s="160"/>
+      <c r="B7" s="158"/>
       <c r="C7" s="99" t="s">
         <v>29</v>
       </c>
@@ -8115,27 +8115,27 @@
     </row>
     <row r="11" spans="1:22" ht="15" x14ac:dyDescent="0.25">
       <c r="A11" s="94"/>
-      <c r="B11" s="161" t="s">
+      <c r="B11" s="156" t="s">
         <v>37</v>
       </c>
-      <c r="C11" s="162"/>
-      <c r="D11" s="155" t="s">
+      <c r="C11" s="157"/>
+      <c r="D11" s="160" t="s">
         <v>31</v>
       </c>
-      <c r="E11" s="156"/>
-      <c r="F11" s="156"/>
-      <c r="G11" s="157"/>
+      <c r="E11" s="161"/>
+      <c r="F11" s="161"/>
+      <c r="G11" s="162"/>
       <c r="H11" s="94"/>
-      <c r="I11" s="161" t="s">
+      <c r="I11" s="156" t="s">
         <v>38</v>
       </c>
-      <c r="J11" s="162"/>
-      <c r="K11" s="155" t="s">
+      <c r="J11" s="157"/>
+      <c r="K11" s="160" t="s">
         <v>31</v>
       </c>
-      <c r="L11" s="156"/>
-      <c r="M11" s="156"/>
-      <c r="N11" s="157"/>
+      <c r="L11" s="161"/>
+      <c r="M11" s="161"/>
+      <c r="N11" s="162"/>
       <c r="O11" s="94"/>
       <c r="P11" s="94"/>
       <c r="Q11" s="94"/>
@@ -8147,8 +8147,8 @@
     </row>
     <row r="12" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="94"/>
-      <c r="B12" s="160"/>
-      <c r="C12" s="163"/>
+      <c r="B12" s="158"/>
+      <c r="C12" s="159"/>
       <c r="D12" s="96" t="s">
         <v>32</v>
       </c>
@@ -8162,8 +8162,8 @@
         <v>29</v>
       </c>
       <c r="H12" s="94"/>
-      <c r="I12" s="160"/>
-      <c r="J12" s="163"/>
+      <c r="I12" s="158"/>
+      <c r="J12" s="159"/>
       <c r="K12" s="97" t="s">
         <v>27</v>
       </c>
@@ -8187,7 +8187,7 @@
     </row>
     <row r="13" spans="1:22" ht="15" x14ac:dyDescent="0.25">
       <c r="A13" s="94"/>
-      <c r="B13" s="158" t="s">
+      <c r="B13" s="163" t="s">
         <v>30</v>
       </c>
       <c r="C13" s="95" t="s">
@@ -8206,7 +8206,7 @@
         <v>92.74</v>
       </c>
       <c r="H13" s="94"/>
-      <c r="I13" s="158" t="s">
+      <c r="I13" s="163" t="s">
         <v>30</v>
       </c>
       <c r="J13" s="95" t="s">
@@ -8235,7 +8235,7 @@
     </row>
     <row r="14" spans="1:22" ht="15" x14ac:dyDescent="0.25">
       <c r="A14" s="94"/>
-      <c r="B14" s="159"/>
+      <c r="B14" s="164"/>
       <c r="C14" s="96" t="s">
         <v>28</v>
       </c>
@@ -8252,7 +8252,7 @@
         <v>91.3</v>
       </c>
       <c r="H14" s="94"/>
-      <c r="I14" s="159"/>
+      <c r="I14" s="164"/>
       <c r="J14" s="96" t="s">
         <v>28</v>
       </c>
@@ -8279,7 +8279,7 @@
     </row>
     <row r="15" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="94"/>
-      <c r="B15" s="160"/>
+      <c r="B15" s="158"/>
       <c r="C15" s="99" t="s">
         <v>29</v>
       </c>
@@ -8296,7 +8296,7 @@
         <v>88.35</v>
       </c>
       <c r="H15" s="94"/>
-      <c r="I15" s="160"/>
+      <c r="I15" s="158"/>
       <c r="J15" s="99" t="s">
         <v>29</v>
       </c>
@@ -8347,44 +8347,44 @@
     </row>
     <row r="17" spans="1:22" ht="15" x14ac:dyDescent="0.25">
       <c r="A17" s="94"/>
-      <c r="B17" s="161" t="s">
+      <c r="B17" s="156" t="s">
         <v>36</v>
       </c>
-      <c r="C17" s="162"/>
-      <c r="D17" s="155" t="s">
+      <c r="C17" s="157"/>
+      <c r="D17" s="160" t="s">
         <v>31</v>
       </c>
-      <c r="E17" s="156"/>
-      <c r="F17" s="156"/>
-      <c r="G17" s="157"/>
+      <c r="E17" s="161"/>
+      <c r="F17" s="161"/>
+      <c r="G17" s="162"/>
       <c r="H17" s="94"/>
-      <c r="I17" s="161" t="s">
+      <c r="I17" s="156" t="s">
         <v>35</v>
       </c>
-      <c r="J17" s="162"/>
-      <c r="K17" s="155" t="s">
+      <c r="J17" s="157"/>
+      <c r="K17" s="160" t="s">
         <v>31</v>
       </c>
-      <c r="L17" s="156"/>
-      <c r="M17" s="156"/>
-      <c r="N17" s="157"/>
+      <c r="L17" s="161"/>
+      <c r="M17" s="161"/>
+      <c r="N17" s="162"/>
       <c r="O17" s="94"/>
-      <c r="P17" s="161" t="s">
+      <c r="P17" s="156" t="s">
         <v>34</v>
       </c>
-      <c r="Q17" s="162"/>
-      <c r="R17" s="155" t="s">
+      <c r="Q17" s="157"/>
+      <c r="R17" s="160" t="s">
         <v>31</v>
       </c>
-      <c r="S17" s="156"/>
-      <c r="T17" s="156"/>
-      <c r="U17" s="157"/>
+      <c r="S17" s="161"/>
+      <c r="T17" s="161"/>
+      <c r="U17" s="162"/>
       <c r="V17" s="94"/>
     </row>
     <row r="18" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="94"/>
-      <c r="B18" s="160"/>
-      <c r="C18" s="163"/>
+      <c r="B18" s="158"/>
+      <c r="C18" s="159"/>
       <c r="D18" s="96" t="s">
         <v>32</v>
       </c>
@@ -8398,8 +8398,8 @@
         <v>29</v>
       </c>
       <c r="H18" s="94"/>
-      <c r="I18" s="160"/>
-      <c r="J18" s="163"/>
+      <c r="I18" s="158"/>
+      <c r="J18" s="159"/>
       <c r="K18" s="97" t="s">
         <v>27</v>
       </c>
@@ -8413,8 +8413,8 @@
         <v>32</v>
       </c>
       <c r="O18" s="94"/>
-      <c r="P18" s="160"/>
-      <c r="Q18" s="163"/>
+      <c r="P18" s="158"/>
+      <c r="Q18" s="159"/>
       <c r="R18" s="97" t="s">
         <v>27</v>
       </c>
@@ -8431,7 +8431,7 @@
     </row>
     <row r="19" spans="1:22" ht="15" x14ac:dyDescent="0.25">
       <c r="A19" s="94"/>
-      <c r="B19" s="158" t="s">
+      <c r="B19" s="163" t="s">
         <v>30</v>
       </c>
       <c r="C19" s="95" t="s">
@@ -8450,7 +8450,7 @@
         <v>91.16</v>
       </c>
       <c r="H19" s="94"/>
-      <c r="I19" s="158" t="s">
+      <c r="I19" s="163" t="s">
         <v>30</v>
       </c>
       <c r="J19" s="95" t="s">
@@ -8469,7 +8469,7 @@
         <v>76.89</v>
       </c>
       <c r="O19" s="94"/>
-      <c r="P19" s="158" t="s">
+      <c r="P19" s="163" t="s">
         <v>30</v>
       </c>
       <c r="Q19" s="95" t="s">
@@ -8491,7 +8491,7 @@
     </row>
     <row r="20" spans="1:22" ht="15" x14ac:dyDescent="0.25">
       <c r="A20" s="94"/>
-      <c r="B20" s="159"/>
+      <c r="B20" s="164"/>
       <c r="C20" s="96" t="s">
         <v>28</v>
       </c>
@@ -8508,7 +8508,7 @@
         <v>89.93</v>
       </c>
       <c r="H20" s="94"/>
-      <c r="I20" s="159"/>
+      <c r="I20" s="164"/>
       <c r="J20" s="96" t="s">
         <v>28</v>
       </c>
@@ -8525,7 +8525,7 @@
         <v>72.8</v>
       </c>
       <c r="O20" s="94"/>
-      <c r="P20" s="159"/>
+      <c r="P20" s="164"/>
       <c r="Q20" s="96" t="s">
         <v>28</v>
       </c>
@@ -8545,7 +8545,7 @@
     </row>
     <row r="21" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="94"/>
-      <c r="B21" s="160"/>
+      <c r="B21" s="158"/>
       <c r="C21" s="99" t="s">
         <v>29</v>
       </c>
@@ -8562,7 +8562,7 @@
         <v>87.1</v>
       </c>
       <c r="H21" s="94"/>
-      <c r="I21" s="160"/>
+      <c r="I21" s="158"/>
       <c r="J21" s="99" t="s">
         <v>29</v>
       </c>
@@ -8579,7 +8579,7 @@
         <v>74.819999999999993</v>
       </c>
       <c r="O21" s="94"/>
-      <c r="P21" s="160"/>
+      <c r="P21" s="158"/>
       <c r="Q21" s="99" t="s">
         <v>29</v>
       </c>
@@ -8623,11 +8623,6 @@
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="P17:Q18"/>
-    <mergeCell ref="R17:U17"/>
-    <mergeCell ref="B19:B21"/>
-    <mergeCell ref="I19:I21"/>
-    <mergeCell ref="P19:P21"/>
     <mergeCell ref="D3:G3"/>
     <mergeCell ref="D11:G11"/>
     <mergeCell ref="D17:G17"/>
@@ -8641,6 +8636,11 @@
     <mergeCell ref="B5:B7"/>
     <mergeCell ref="B11:C12"/>
     <mergeCell ref="I11:J12"/>
+    <mergeCell ref="P17:Q18"/>
+    <mergeCell ref="R17:U17"/>
+    <mergeCell ref="B19:B21"/>
+    <mergeCell ref="I19:I21"/>
+    <mergeCell ref="P19:P21"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="D5:D7">
